--- a/upload_sca.xlsx
+++ b/upload_sca.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4528CD23-0B71-4550-B5C4-B97F17EB6484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="data" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="24012026" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase">#REF!</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="599">
   <si>
     <t>pickup_name</t>
   </si>
@@ -81,19 +78,1753 @@
   </si>
   <si>
     <t>pickup_cust_no</t>
+  </si>
+  <si>
+    <t>ST EG ADVENTURE STORE RADIO DALAM</t>
+  </si>
+  <si>
+    <t>EIGER</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CGK000</t>
+  </si>
+  <si>
+    <t>CGK10000</t>
+  </si>
+  <si>
+    <t>REG</t>
+  </si>
+  <si>
+    <t>80561504_CT08PROEIGER18FEB20266FQF5256</t>
+  </si>
+  <si>
+    <t>EIGER ADVENTURE STORE RADIO DALAMJL.RADIO DALAM RAYA NO.80 RT 005 RW 014 , GANDARIA UTARA, KEBAYORAN BARU ,JAKARTA SELATAN DKI JAKARTA 12140</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>21:29</t>
+  </si>
+  <si>
+    <t>MOTOR</t>
+  </si>
+  <si>
+    <t>CORPORATE</t>
+  </si>
+  <si>
+    <t>A. ADHI.P</t>
+  </si>
+  <si>
+    <t>087877945726</t>
+  </si>
+  <si>
+    <t>ASURANSI + -</t>
+  </si>
+  <si>
+    <t>MCD SUKAHATI CIBINONG</t>
+  </si>
+  <si>
+    <t>80561504</t>
+  </si>
+  <si>
+    <t>80561504_CT08PROEIGER18FEB2026S43X2837</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>80561504_CT08PROEIGER18FEB202697XG9492</t>
+  </si>
+  <si>
+    <t>80561504_CT08PROEIGER18FEB2026U6IR8936</t>
+  </si>
+  <si>
+    <t>80561504_CT08PROEIGER18FEB202638LW9130</t>
+  </si>
+  <si>
+    <t>21:31</t>
+  </si>
+  <si>
+    <t>80561504_CT08PROEIGER18FEB20267N499091</t>
+  </si>
+  <si>
+    <t>21:32</t>
+  </si>
+  <si>
+    <t>80561504_CT08PROEIGER18FEB2026RWPC4115</t>
+  </si>
+  <si>
+    <t>21:34</t>
+  </si>
+  <si>
+    <t>80561504_CT08PROEIGER18FEB2026NL9B7400</t>
+  </si>
+  <si>
+    <t>21:37</t>
+  </si>
+  <si>
+    <t>BENANG JARUM SENAYAN CITY</t>
+  </si>
+  <si>
+    <t>BUTTONSCARVES PICK UP OFFLINE</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>80887103_CT08PROBUTTONSCARVESPICKUPOFFLINE25FEB20262UI8</t>
+  </si>
+  <si>
+    <t>BENANG JARUM SENAYAN CITTY LT 2 DEPAN OPTIK MELAWAI</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>21:43</t>
+  </si>
+  <si>
+    <t>DISTI ANGGRAENI</t>
+  </si>
+  <si>
+    <t>089517204706</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + </t>
+  </si>
+  <si>
+    <t>4 SERLY AUDIANA 62 85368230322 JL RAYA CENGKEH NO08 RT001 RW</t>
+  </si>
+  <si>
+    <t>80887103</t>
+  </si>
+  <si>
+    <t>NO:DIP/LGS/I/2026/198-BP LEONARDO FAHDI OKTAVIAN</t>
+  </si>
+  <si>
+    <t>DATINDO</t>
+  </si>
+  <si>
+    <t>MJK000</t>
+  </si>
+  <si>
+    <t>MJK10000</t>
+  </si>
+  <si>
+    <t>80090800_CT08PRODATINDO25FEB2026I45O</t>
+  </si>
+  <si>
+    <t>DUSUN SIDOBECIK RT 002 RW 007 DESA PULOREJO KECAMATAN DAWARBLANDONG KABUPATEN MOJOKERTO JAWA TIMUR 61354 SEBERANG MUSHOLA AL HIDAYAH</t>
+  </si>
+  <si>
+    <t>22:19</t>
+  </si>
+  <si>
+    <t>MOBIL</t>
+  </si>
+  <si>
+    <t>085748495799</t>
+  </si>
+  <si>
+    <t>ASURANSI PACKING KAYU + 5 000000</t>
+  </si>
+  <si>
+    <t>PTDATINDO INFONET PRIMA KOMPLEK HARMONI PLAZA BLOK G NO 68 J</t>
+  </si>
+  <si>
+    <t>80090800</t>
+  </si>
+  <si>
+    <t>CAR MATARAM</t>
+  </si>
+  <si>
+    <t>AJ CAR</t>
+  </si>
+  <si>
+    <t>AMI000</t>
+  </si>
+  <si>
+    <t>AMI10000</t>
+  </si>
+  <si>
+    <t>80541001_CT08PROAJCAR25FEB20268FC6</t>
+  </si>
+  <si>
+    <t>JL PANCA USAHA NO25B CILINAYA CAKRANEGARA LOMBOK 83239 INDONESIA</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>YANI</t>
+  </si>
+  <si>
+    <t>62 370 622650 62 370</t>
+  </si>
+  <si>
+    <t>80541001</t>
+  </si>
+  <si>
+    <t>NEW BALANCE DUTAMALL PALANGKARAYA</t>
+  </si>
+  <si>
+    <t>MAA MANUAL (EMAIL)</t>
+  </si>
+  <si>
+    <t>PKY000</t>
+  </si>
+  <si>
+    <t>PKY10000</t>
+  </si>
+  <si>
+    <t>80541301_CT08PROMAAMANUAL(EMAIL)24JAN2026E93G5390</t>
+  </si>
+  <si>
+    <t>JLN. ADONIS SAMAD , DUTA MALL UGF / C-015 KELURAHAN LANGKAI KECAMATAN PAHANDUT KOTA PALANGKARAYA  73111</t>
+  </si>
+  <si>
+    <t>2026-01-24</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>MAA ACTIVE MANUAL</t>
+  </si>
+  <si>
+    <t>082266052989</t>
+  </si>
+  <si>
+    <t>ASURANSI + 1.699.000</t>
+  </si>
+  <si>
+    <t>FELISIA DAMAYANTI =&gt; JL. SETRA DAGO UTARA RAYA NO. 15,  ANTA</t>
+  </si>
+  <si>
+    <t>80541301</t>
+  </si>
+  <si>
+    <t>PT ARINA PARAMA JAYA</t>
+  </si>
+  <si>
+    <t>TOYOTA ASTRA MOTOR</t>
+  </si>
+  <si>
+    <t>SUB000</t>
+  </si>
+  <si>
+    <t>SUB10000</t>
+  </si>
+  <si>
+    <t>80078100_CT08PROTOYOTAASTRAMOTOR24JAN2026AO290439</t>
+  </si>
+  <si>
+    <t>RAYA VETERAN KM 1 GRESIK</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>SONNY</t>
+  </si>
+  <si>
+    <t>081559572563</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + 2.700.000</t>
+  </si>
+  <si>
+    <t>PT.TOYOTA ASTRA MOTOR JL.GAYA MOTOR SELATAN NO.5,SUNTER II J</t>
+  </si>
+  <si>
+    <t>80078100</t>
+  </si>
+  <si>
+    <t>AUTO 2000 SOEKARNO HATTA</t>
+  </si>
+  <si>
+    <t>BDO000</t>
+  </si>
+  <si>
+    <t>BDO10000</t>
+  </si>
+  <si>
+    <t>80052600_CT08PROTOYOTAASTRAMOTOR24JAN2026GNSR7990</t>
+  </si>
+  <si>
+    <t>JL. SOEKARNO HATTA NO. 145 BANDUNG</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>GUN GUN GUNAWAN</t>
+  </si>
+  <si>
+    <t>081320346727</t>
+  </si>
+  <si>
+    <t>ASURANSI + PACKING KAYU + RP. 15.440.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT.TOYOTA-ASTRA MOTOR JL. GAYA MOTOR SELATAN NO.5 SUNTER-II </t>
+  </si>
+  <si>
+    <t>80052600</t>
+  </si>
+  <si>
+    <t>MR DALIP</t>
+  </si>
+  <si>
+    <t>ANDALAN EXPRESS</t>
+  </si>
+  <si>
+    <t>80537601_CT08PROANDALANEXPRESS24JAN2026FFZ84707</t>
+  </si>
+  <si>
+    <t>PD SAUDARA JIN. MAYOR SUNARYA NO.16(G6 TAMIM) BANDUNG40181.NDONESIA BANDUNG 40181</t>
+  </si>
+  <si>
+    <t>09:36</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>62224205276</t>
+  </si>
+  <si>
+    <t>DARSHAN KUMAR JL HARAPAN JAYA NO 43 CEMPAKABARU JAKARTA PUSA</t>
+  </si>
+  <si>
+    <t>80537601</t>
+  </si>
+  <si>
+    <t>PT INTIKOM BERLIAN MUSTIKA</t>
+  </si>
+  <si>
+    <t>INTIKOM BERLIAN MUSTIKA / LOGI</t>
+  </si>
+  <si>
+    <t>80640300_CT08PROINTIKOMBERLIANMUSTIKA/LOGI24JAN2026N57G1023</t>
+  </si>
+  <si>
+    <t>JL DUREN TIGA RAYA NO 32 RT3/RW5 DUREN  TIGA, KEC.PANCORAN KOTA JAKARTA SELATAN,DAERAH KHUSUS  IBUKOTA JAKARTA 12760</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>MALIK</t>
+  </si>
+  <si>
+    <t>0895321888881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACKING KAYU + </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCA KCU CILACAP  JL. JEND. AHMAD YANI NO.118, SIDAKAYA DUA, </t>
+  </si>
+  <si>
+    <t>80640300</t>
+  </si>
+  <si>
+    <t>PT BAHANA GENTA VIKTORY</t>
+  </si>
+  <si>
+    <t>REKSO</t>
+  </si>
+  <si>
+    <t>80024018_CT08PROREKSO24JAN202654OP0734</t>
+  </si>
+  <si>
+    <t>JL. KH. HASYIM ASHARI NO.1A, RT.2/RW.5, PETOJO UTARA, KECAMATAN GAMBIR , KOTA JAKARTA PUSAT, DAERAH KHUSUS IBUKOTA JAKARTA 10130.</t>
+  </si>
+  <si>
+    <t>RANTI</t>
+  </si>
+  <si>
+    <t>087784336316</t>
+  </si>
+  <si>
+    <t>MCD SOEKARNO HATTA BANDUNG JL.SOEKARNO HATTA NO.611 RT.01</t>
+  </si>
+  <si>
+    <t>80024018</t>
+  </si>
+  <si>
+    <t>AUTO 2000 MALANG SUTOYO</t>
+  </si>
+  <si>
+    <t>MXG000</t>
+  </si>
+  <si>
+    <t>MXG10000</t>
+  </si>
+  <si>
+    <t>80052600 _CT08PROTOYOTAASTRAMOTOR24JAN2026W3251815</t>
+  </si>
+  <si>
+    <t>AUTO 2000 MALANG SUTOYO JL. LETJEND. SUTOYO NO.25  MALANG</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>SUPRIADI</t>
+  </si>
+  <si>
+    <t>08123381750</t>
+  </si>
+  <si>
+    <t>ASURANSI + PACKING KAYU + RP8,000,000</t>
+  </si>
+  <si>
+    <t>PT. TOYOTA ASTRA MOTOR  TECHNICAL SERVICE DIVISION FIELD ACT</t>
+  </si>
+  <si>
+    <t>PT TUNAS AUTO GRAHA</t>
+  </si>
+  <si>
+    <t>PLM000</t>
+  </si>
+  <si>
+    <t>PLM10000</t>
+  </si>
+  <si>
+    <t>80062000_CT08PROTOYOTAASTRAMOTOR24JAN2026Q4BY8675</t>
+  </si>
+  <si>
+    <t>JL. PERINTIS KEMERDEKAAN NO. 8 PALEMBANG</t>
+  </si>
+  <si>
+    <t>YUDI</t>
+  </si>
+  <si>
+    <t>081272367880</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + 1.180.000</t>
+  </si>
+  <si>
+    <t>80062000</t>
+  </si>
+  <si>
+    <t>ZARA SENAYAN CITY</t>
+  </si>
+  <si>
+    <t>ZARA</t>
+  </si>
+  <si>
+    <t>80536501_CT08PROZARA24JAN2026TP044230</t>
+  </si>
+  <si>
+    <t>JL. ASIA AFRIKA NO.8, RT.1/RW.3, GELORA, KECAMATAN TANAH ABANG, KOTA JAKARTA PUSAT, DAERAH KHUSUS IBUKOTA JAKARTA 10270</t>
+  </si>
+  <si>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>MS YUNI</t>
+  </si>
+  <si>
+    <t>62 878 7514 8077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PICKUP JAM 16:00 - + </t>
+  </si>
+  <si>
+    <t>80536501</t>
+  </si>
+  <si>
+    <t>HYPERMART FLAGSHIP STORE</t>
+  </si>
+  <si>
+    <t>GLOBAL DIGITAL NIAGA TBK PT</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>80030200_CT08PROGLOBALDIGITALNIAGATBKPT24JAN2026BLCF5168</t>
+  </si>
+  <si>
+    <t>MALL MATAHARI DAAN MOGOT LT.1 JL. RAYA DAAN MOGOT KM. 16.5 KARET 8 12, RT.8/RW.12, KALIDERES, KEC. KALIDERES, KOTA JAKARTA BARAT, DAERAH KHUSUS IBUKOTA JAKARTA 12920 KOTA JAKARTA BARAT 11840 DKI JAKARTA</t>
+  </si>
+  <si>
+    <t>80030200</t>
+  </si>
+  <si>
+    <t>VIVA APOTEK FLAGSHIP STORE</t>
+  </si>
+  <si>
+    <t>BKI000</t>
+  </si>
+  <si>
+    <t>BKI10000</t>
+  </si>
+  <si>
+    <t>CTC23</t>
+  </si>
+  <si>
+    <t>80030200_CT08PROGLOBALDIGITALNIAGATBKPT24JAN2026H6ZH1392</t>
+  </si>
+  <si>
+    <t>GG. ALNUSA NO.15, RT.004/RW.006, JATIRANGGON, KEC. JATISAMPURNA, KOTA BKS, JAWA BARAT 17432, INDONESIA KOTA BEKASI 17432 JAWA BARAT</t>
+  </si>
+  <si>
+    <t>VIVA APOTEK HANKAM</t>
+  </si>
+  <si>
+    <t>6282246545251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y + </t>
+  </si>
+  <si>
+    <t>VIVA APOTEK GRAHA RAYA</t>
+  </si>
+  <si>
+    <t>TGR000</t>
+  </si>
+  <si>
+    <t>TGR10000</t>
+  </si>
+  <si>
+    <t>80030200_CT08PROGLOBALDIGITALNIAGATBKPT24JAN2026BMPD7164</t>
+  </si>
+  <si>
+    <t>RUKO VENICE ARCADE, JL. BOULEVARD GRAHA RAYA NO.11, BINTARO, PAKU JAYA, KEC. SERPONG UTARA, KOTA TANGERANG SELATAN, BANTEN 15220, INDONESIA KOTA TANGERANG SELA 15324 BANTEN</t>
+  </si>
+  <si>
+    <t>6285282618321</t>
+  </si>
+  <si>
+    <t>8811622507808171</t>
+  </si>
+  <si>
+    <t>TOSHIBA FLAGSHIP STORE</t>
+  </si>
+  <si>
+    <t>80030200_CT08PROGLOBALDIGITALNIAGATBKPT24JAN2026UA5W4890</t>
+  </si>
+  <si>
+    <t>KOMPLEK PERGUDANGAN CARDIG CARGO CENTER RT.1/RW.9, HALIM PERDANA KUSUMAH, KEC. MAKASAR, KOTA JAKARTA TIMUR, DAERAH KHUSUS IBUKOTA JAKARTA 13650 KOTA JAKARTA TIMUR 13610 DKI JAKARTA</t>
+  </si>
+  <si>
+    <t>ROBBY SURYO</t>
+  </si>
+  <si>
+    <t>6281803240681</t>
+  </si>
+  <si>
+    <t>8811622506254914</t>
+  </si>
+  <si>
+    <t>POLYTRON FLAGSHIP STORE</t>
+  </si>
+  <si>
+    <t>JTR23</t>
+  </si>
+  <si>
+    <t>80030200_CT08PROGLOBALDIGITALNIAGATBKPT24JAN202653KY3376</t>
+  </si>
+  <si>
+    <t>JL. RAYA SERANG KM 14,5 , DESA PASIR GADUNG RT.001 RW.001 , KEC. CIKUPA, KABUPATEN TANGERANG, BANTEN 15710, INDONESIA KAB. TANGERANG 15710 BANTEN</t>
+  </si>
+  <si>
+    <t>09:44</t>
+  </si>
+  <si>
+    <t>SIN KIAN</t>
+  </si>
+  <si>
+    <t>6287781154677</t>
+  </si>
+  <si>
+    <t>8811622506256448</t>
+  </si>
+  <si>
+    <t>PULL&amp;BEAR PAKUWON MALL</t>
+  </si>
+  <si>
+    <t>PULL&amp;BEAR</t>
+  </si>
+  <si>
+    <t>80556101_CT08PROPULL&amp;BEAR24JAN2026POGE9710</t>
+  </si>
+  <si>
+    <t>PAKUWON MALL LT. LG UNIT 69,70,73 &amp; 75. JL. MAYJEN YONO SUWOYO NO.2, BABATAN, KEC. WIYUNG, KOTA SBY, JAWA TIMUR. KODE POS : 60227</t>
+  </si>
+  <si>
+    <t>HANI</t>
+  </si>
+  <si>
+    <t>03199148046</t>
+  </si>
+  <si>
+    <t>- + -</t>
+  </si>
+  <si>
+    <t>80556101</t>
+  </si>
+  <si>
+    <t>CAHYA (13:00 - 17:00)</t>
+  </si>
+  <si>
+    <t>PT GEULIS BUSANA KREASINDO</t>
+  </si>
+  <si>
+    <t>81086300_CT08PROPTGEULISBUSANAKREASINDO24JAN2026RLYQ4268</t>
+  </si>
+  <si>
+    <t>GOLF ISLAND , RUKAN THE BEACH 2 BOULEVARD BLOK RB2B NO . 005 KEL. : KEC. : ULEE KARENG KOTA MADYA/KOTA : DAERAH KHUSUS IBUKOTA JAKARTA</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>CAHYA</t>
+  </si>
+  <si>
+    <t>089651355493</t>
+  </si>
+  <si>
+    <t>ASURANSI + 300.000</t>
+  </si>
+  <si>
+    <t>GEULIS / WIDIA +62 85646175148 TUNJUNGAN PLAZA 3 LT 3 NO 1 -</t>
+  </si>
+  <si>
+    <t>81086300</t>
+  </si>
+  <si>
+    <t>LAILY ASHRY</t>
+  </si>
+  <si>
+    <t>BLIBLI RETURN</t>
+  </si>
+  <si>
+    <t>DPS000</t>
+  </si>
+  <si>
+    <t>DPS10000</t>
+  </si>
+  <si>
+    <t>JNE TRUCKING</t>
+  </si>
+  <si>
+    <t>80508108_CT08PROBLIBLI RETURN24JAN202617MM0003</t>
+  </si>
+  <si>
+    <t>JL. GRIYA NAMBI PERMAI NO.14, UBUNG KAJA, KEC. DENPASAR UTARA, C, BALI 80115, INDONESIA DENPASAR UTARA - UBUNG KAJA BALI 80115</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>BLIND VAN</t>
+  </si>
+  <si>
+    <t>ASURANSI + 394000</t>
+  </si>
+  <si>
+    <t>WAREHOUSE RETURN SURABAYA JL. BERBEK INDUSTRI I NO. 5-19 WAR</t>
+  </si>
+  <si>
+    <t>80508108</t>
+  </si>
+  <si>
+    <t>ROXY FULFILLMENT CENTER</t>
+  </si>
+  <si>
+    <t>BERBAGI INOVASI TEKNOLOGI PT</t>
+  </si>
+  <si>
+    <t>REGULER</t>
+  </si>
+  <si>
+    <t>80557900_CT08PROBERBAGIINOVASITEKNOLOGIPT24JAN2026XUOJ2253</t>
+  </si>
+  <si>
+    <t>JALAN PETOJO VIY II, MASUK DARI JL. TERNATE NO.24D, CIDENG, KECAMATAN GAMBIR, KOTA JAKARTA PUSAT, JAKARTA 10130 JAKARTA PUSAT 10140 DKI JAKARTA</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>ROXY FULFILLMENT CENTER [PT H</t>
+  </si>
+  <si>
+    <t>08112346680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N + </t>
+  </si>
+  <si>
+    <t>80557900</t>
+  </si>
+  <si>
+    <t>PULL&amp;BEAR PONDOK INDAH MALL</t>
+  </si>
+  <si>
+    <t>80556101_CT08PROPULL&amp;BEAR24JAN2026ZMDF0394</t>
+  </si>
+  <si>
+    <t>JL. METRO PONDOK INDAH KAV. IV, RT.1/RW.16, PD. PINANG, KEC. KBY. LAMA 4, DAERAH KHUSUS IBUKOTA JAKARTA 12310</t>
+  </si>
+  <si>
+    <t>BILAL</t>
+  </si>
+  <si>
+    <t>021 75921047</t>
+  </si>
+  <si>
+    <t>PICKUP JAM 16:00 + -</t>
+  </si>
+  <si>
+    <t>POP UP STORE MELISSA K MALL</t>
+  </si>
+  <si>
+    <t>SEMBILAN OHM</t>
+  </si>
+  <si>
+    <t>81472000_CT08PROSEMBILANOHM24JAN2026HBZE9696</t>
+  </si>
+  <si>
+    <t>K MALL AT MENARA JAKARTA LT GF KOMPLEK, JL. KOTA BARU BANDAR KEMAYORAN NO.C8, GN. SAHARI SEL., KEC. KEMAYORAN, KOTA JAKARTA PUSAT, DAERAH KHUSUS IBUKOTA JAKARTA 10610</t>
+  </si>
+  <si>
+    <t>10:06</t>
+  </si>
+  <si>
+    <t>SULIS</t>
+  </si>
+  <si>
+    <t>62 87799449050</t>
+  </si>
+  <si>
+    <t>ASURANSI + 550,000</t>
+  </si>
+  <si>
+    <t>NOVITA ALAMAT EMAIL : ALAMAT LENGKAP : JL.GAJAHMADA 99B (KAN</t>
+  </si>
+  <si>
+    <t>81472000</t>
+  </si>
+  <si>
+    <t>PULL&amp;BEAR GRAND INDONESIA</t>
+  </si>
+  <si>
+    <t>80556101_CT08PROPULL&amp;BEAR24JAN2026QWI23588</t>
+  </si>
+  <si>
+    <t>MALL GRAND INDONESIA JL. M.H. THAMRIN NO.1, MENTENG, KEC. MENTENG, KOTA JAKARTA PUSAT, DAERAH KHUSUS IBUKOTA JAKARTA 10310</t>
+  </si>
+  <si>
+    <t>CIA</t>
+  </si>
+  <si>
+    <t>021 85703997635</t>
+  </si>
+  <si>
+    <t>ARDY (13:00 - 17:00)</t>
+  </si>
+  <si>
+    <t>81086300_CT08PROPTGEULISBUSANAKREASINDO24JAN2026SO8E3250</t>
+  </si>
+  <si>
+    <t>GOLF ISLAND, RUKAN THE BEACH 2 BOULEVARD BLOK RB2B NOMOR 005, DAERAH KHUSUS IBUKOTA JAKARTA</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>GEULIS</t>
+  </si>
+  <si>
+    <t>62 88975367576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOHON HUBUNGI NO HP TERLAMPIR SEBELUM PICK UP + </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT. ARRO MITSU MANDIRI (IKA / ROTUA 081513257335) PERUMAHAN </t>
+  </si>
+  <si>
+    <t>JAKARTA HOUSEWARES</t>
+  </si>
+  <si>
+    <t>80030200_CT08PROGLOBALDIGITALNIAGATBKPT24JAN2026H4800212</t>
+  </si>
+  <si>
+    <t>CITRA 2 EXT BLOK BG2C NO 20 KOTA JAKARTA BARAT 11830 DKI JAKARTA</t>
+  </si>
+  <si>
+    <t>10:28</t>
+  </si>
+  <si>
+    <t>FEMMY</t>
+  </si>
+  <si>
+    <t>085694640935</t>
+  </si>
+  <si>
+    <t>8811622507798802</t>
+  </si>
+  <si>
+    <t>BUTTONSCARVES RIAU BANDUNG</t>
+  </si>
+  <si>
+    <t>80890503_CT08PROBUTTONSCARVESPICKUPOFFLINE24JAN2026TKHO6553</t>
+  </si>
+  <si>
+    <t>BUTTONSCARVES JL. LLRE MARTADINATA NO.34 CITARUM, KEC. BANDUNG WETAN, KOTA BANDUNG, JAWA BARAT 40115</t>
+  </si>
+  <si>
+    <t>FITRI NURAENI</t>
+  </si>
+  <si>
+    <t>081564764871</t>
+  </si>
+  <si>
+    <t>NAMA SITI SOFIA NO 085136489350 ALAMAT TANJUNG PASIR RT/RW 0</t>
+  </si>
+  <si>
+    <t>80890503</t>
+  </si>
+  <si>
+    <t>STORE NADA PUSPITA PIM 2</t>
+  </si>
+  <si>
+    <t>80887303_CT08PROBUTTONSCARVESPICKUPOFFLINE24JAN2026YTM19879</t>
+  </si>
+  <si>
+    <t>NADA PUSPITA PIM 2 LT.2, PONDOK INDAH MALL 2 , LANTAI 2 , UNIT 211 , JL. METRO PONDOK INDAH, PD.PINANG, KEC. KBY LAMA, JAKARTA SELATAN</t>
+  </si>
+  <si>
+    <t>ELSYA</t>
+  </si>
+  <si>
+    <t>089653417136</t>
+  </si>
+  <si>
+    <t>BUATKAN AWB MANUAL + -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. ISMA NO TLPN: 0811-2316-179 ALAMAT: KOMPLEK DUTA REGENCY </t>
+  </si>
+  <si>
+    <t>80887303</t>
+  </si>
+  <si>
+    <t>80887303_CT08PROBUTTONSCARVESPICKUPOFFLINE24JAN2026WSJK7218</t>
+  </si>
+  <si>
+    <t>2. TITANIA DWI SARTIKA NOTLPN:0857-2599-9667 ALAMAT: CLUSTER</t>
+  </si>
+  <si>
+    <t>PULL&amp;BEAR DELIPARK MEDAN</t>
+  </si>
+  <si>
+    <t>MES000</t>
+  </si>
+  <si>
+    <t>MES10000</t>
+  </si>
+  <si>
+    <t>80556101_CT08PROPULL&amp;BEAR24JAN2026K61G4691</t>
+  </si>
+  <si>
+    <t>G FLOOR, MALL DELI PARK, JALAN GURU PATIMPUS BLOK OPQ NO.1, KESAWAN, WEST MEDAN, MEDAN CITY, NORTH SUMATRA 20111</t>
+  </si>
+  <si>
+    <t>10:29</t>
+  </si>
+  <si>
+    <t>ANGGI</t>
+  </si>
+  <si>
+    <t>061 62000726</t>
+  </si>
+  <si>
+    <t>ZARA TRANS STUDIO MALL MAKASSAR</t>
+  </si>
+  <si>
+    <t>UPG000</t>
+  </si>
+  <si>
+    <t>UPG10000</t>
+  </si>
+  <si>
+    <t>80536500_CT08PROZARA24JAN20263V3A4040</t>
+  </si>
+  <si>
+    <t>TRANS STUDIO MALL, MACCINI SOMBALA, KEC. TAMALATE, KOTA MAKASSAR, SULAWESI SELATAN 90224</t>
+  </si>
+  <si>
+    <t>10:39</t>
+  </si>
+  <si>
+    <t>HARRY</t>
+  </si>
+  <si>
+    <t>62 85158851771</t>
+  </si>
+  <si>
+    <t>80536500</t>
+  </si>
+  <si>
+    <t>EIGER TEBET</t>
+  </si>
+  <si>
+    <t>80561504_CT08PROEIGER24JAN20268LQB2231</t>
+  </si>
+  <si>
+    <t>EIGER TEBET JAKARTA SELATAN  JL. TEBET RAYA NO.38B, RT.03/RW.4, TEBET TIM., KEC. TEBET, KOTA JAKARTA SELATAN, DAERAH KHUSUS IBUKOTA JAKARTA 12820</t>
+  </si>
+  <si>
+    <t>081120011475</t>
+  </si>
+  <si>
+    <t>TORY BURCH SENAYAN CITY</t>
+  </si>
+  <si>
+    <t>SENTRALWATCH</t>
+  </si>
+  <si>
+    <t>80061406_CT08PROSENTRALWATCH24JAN20262VBX2141</t>
+  </si>
+  <si>
+    <t>MALL SENAYAN CITY, JL. ASIA AFRIKA NO.19  GELORA, KECAMATAN TANAH ABANG, KOTA JAKARTA PUSAT, DAERAH KHUSUS IBUKOTA JAKARTA 10270</t>
+  </si>
+  <si>
+    <t>NUKKY</t>
+  </si>
+  <si>
+    <t>087734969590</t>
+  </si>
+  <si>
+    <t>MUTIA RATNASARI ALAMAT : PERMATA DEPOK REGENCY RUBY D12/10 C</t>
+  </si>
+  <si>
+    <t>80061406</t>
+  </si>
+  <si>
+    <t>NADA PUSPITA PEKANBARU</t>
+  </si>
+  <si>
+    <t>PKU000</t>
+  </si>
+  <si>
+    <t>PKU10000</t>
+  </si>
+  <si>
+    <t>JTR</t>
+  </si>
+  <si>
+    <t>80887303_CT08PROBUTTONSCARVESPICKUPOFFLINE24JAN2026SCIW5251</t>
+  </si>
+  <si>
+    <t>NADA PUSPITA PEKANBARU, JL. ARIFIN AHMAD KOMPLEK RUKO PLATINUM BUSINESS CENTRE</t>
+  </si>
+  <si>
+    <t>10:52</t>
+  </si>
+  <si>
+    <t>AJENG</t>
+  </si>
+  <si>
+    <t>082290248338</t>
+  </si>
+  <si>
+    <t>IIS MARYAM NO HP : 08112316179 ALAMAT : KOMPLEK DUTA REGENCY</t>
+  </si>
+  <si>
+    <t>BENANG JARUM PLAZA INDONESIA</t>
+  </si>
+  <si>
+    <t>80887103_CT08PROBUTTONSCARVESPICKUPOFFLINE24JAN202614KO9498</t>
+  </si>
+  <si>
+    <t>BENANG JARUM PLAZA INDONESIA LT.4</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>FATRUNADI RIZKY ILLAHI</t>
+  </si>
+  <si>
+    <t>085772760161</t>
+  </si>
+  <si>
+    <t>1. CLARENCE ALAMAT: JALAN KS TUBUN KOMPLEK SAKURA NO.39 (MAS</t>
+  </si>
+  <si>
+    <t>FOSSIL OUTLET KARAWACI</t>
+  </si>
+  <si>
+    <t>TGR</t>
+  </si>
+  <si>
+    <t>80061401_CT08PROSENTRALWATCH24JAN2026YJTU2089</t>
+  </si>
+  <si>
+    <t>JL.BOULEVARD DIPONEGORO #00-000 LIPPO SUPERMALL KARAWACI LG#83A TANGERANG</t>
+  </si>
+  <si>
+    <t>NENENG YUNENGSIH</t>
+  </si>
+  <si>
+    <t>0215465345</t>
+  </si>
+  <si>
+    <t>RAHADITA CITRA PANTAI MENTARI THE HAMPTON BLOK DD3 NO 27 SUR</t>
+  </si>
+  <si>
+    <t>80061401</t>
+  </si>
+  <si>
+    <t>80061401_CT08PROSENTRALWATCH24JAN2026VFDQ6351</t>
+  </si>
+  <si>
+    <t>KIKY USMAN JL. PANGERAN DIPONEGORO GG. II TOKO KIMIDI CAKE T</t>
+  </si>
+  <si>
+    <t>CV SARIAJI SEJAHTERA</t>
+  </si>
+  <si>
+    <t>SRG000</t>
+  </si>
+  <si>
+    <t>SRG10000</t>
+  </si>
+  <si>
+    <t>80024018_CT08PROREKSO24JAN2026G93W5057</t>
+  </si>
+  <si>
+    <t>JL.MGR SUGIYOPRANOTO 38 SEMARANG</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>DEWI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASURANSI + JANGAN DI BANTING + </t>
+  </si>
+  <si>
+    <t>YOGYAKARTA</t>
+  </si>
+  <si>
+    <t>MBS ACEH - FAST MOVING</t>
+  </si>
+  <si>
+    <t>HALODOC</t>
+  </si>
+  <si>
+    <t>BTJ000</t>
+  </si>
+  <si>
+    <t>BTJ10000</t>
+  </si>
+  <si>
+    <t>81718801_CT08PROHALODOC24JAN20266ZP13583</t>
+  </si>
+  <si>
+    <t>JALAN SOEKARNO HATTA, TINGKUEM, DARUL IMARAH, ACEH BESAR, ACEH, INDONESIA, 23352, KABUPATEN ACEH BESAR, 23352</t>
+  </si>
+  <si>
+    <t>6282277193066</t>
+  </si>
+  <si>
+    <t>5L678Y-2193 APOTIK RAKAN FARMA GAMPA (F) - CD260081292</t>
+  </si>
+  <si>
+    <t>81718801</t>
+  </si>
+  <si>
+    <t>NUGROHO ( PICKUP JAM 12:00 )</t>
+  </si>
+  <si>
+    <t>ANUGRAH SEEK INDONESIA</t>
+  </si>
+  <si>
+    <t>80580500_CT08PROANUGRAHSEEKINDONESIA24JAN2026O50J3095</t>
+  </si>
+  <si>
+    <t>PERGUDANGAN PAKUALAM, BLOK B-7, ALAM SUTRA, SERPONG UTARA, TANGERANG SELATAN. 15320</t>
+  </si>
+  <si>
+    <t>6289526934305</t>
+  </si>
+  <si>
+    <t>80580500</t>
+  </si>
+  <si>
+    <t>EMA/581542314222257575-SELLIN</t>
+  </si>
+  <si>
+    <t>PENARIKAN SAMSUNG</t>
+  </si>
+  <si>
+    <t>CLG000</t>
+  </si>
+  <si>
+    <t>CLG10000</t>
+  </si>
+  <si>
+    <t>80508100_CT08PROPENARIKANSAMSUNG24JAN2026XU9O0881</t>
+  </si>
+  <si>
+    <t>PT. PUTRA TAMBAK UTAMA, NAMBO ILIR, NAMBO ILIR, KIBIN, SERANG, BANTEN, INDONESIA (KP GORDA NAGREG RT 01 RW 05 ),KIBIN,KIBIN,KAB. SERANG,42185 KIBIN KAB. SERANG</t>
+  </si>
+  <si>
+    <t>81286329808</t>
+  </si>
+  <si>
+    <t>80508100</t>
+  </si>
+  <si>
+    <t>AFIFA/2512124YVB8827 / 7323603882</t>
+  </si>
+  <si>
+    <t>BLIBLI PROJECT MANUAL</t>
+  </si>
+  <si>
+    <t>JOG000</t>
+  </si>
+  <si>
+    <t>JOG20400</t>
+  </si>
+  <si>
+    <t>80508100_CT08PROBLIBLIPROJECTMANUAL24JAN20269W649462</t>
+  </si>
+  <si>
+    <t>DUSUN KARANGWULUH LOR KAB. KULON PROGO, KAB. KULON PROGO, DI YOGYAKARTA, 55654,KAB. KULON PROGO,KAB. KULON PROGO,KAB. KULON PROGO,INDONESIA,55654 KULON PROGO KAB. KULON PROGO DI YOGYAKARTA 55654</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>89521733149</t>
+  </si>
+  <si>
+    <t>MELISSA SUN PLAZA MEDAN</t>
+  </si>
+  <si>
+    <t>81472000_CT08PROSEMBILANOHM24JAN202658018607</t>
+  </si>
+  <si>
+    <t>MELISSA SUN PLAZA MEDAN LT.1-B-42 JL. KH. ZAINUL ARIFIN NO.7, MADRAS HULU, MEDAN POLONIA, KOTA MEDAN, SUMATERA UTARA 20152</t>
+  </si>
+  <si>
+    <t>VIENA</t>
+  </si>
+  <si>
+    <t>62 81928076089</t>
+  </si>
+  <si>
+    <t>ASURANSI + 959,900</t>
+  </si>
+  <si>
+    <t>FATHIA AZMI 190482 JALAN ANGGARAN 3 PATUMBAK DELI SERDANG SS</t>
+  </si>
+  <si>
+    <t>BUTTONSCARVES GAIA MALL PONTIANAK</t>
+  </si>
+  <si>
+    <t>PNK000</t>
+  </si>
+  <si>
+    <t>PNK10000</t>
+  </si>
+  <si>
+    <t>80890503_CT08PROBUTTONSCARVESPICKUPOFFLINE24JAN20261ACH9394</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>PANA</t>
+  </si>
+  <si>
+    <t>0895 1801 7117</t>
+  </si>
+  <si>
+    <t>MUHAMMAD IHSANN  NO HP: 085117778853  ALAMAT : JL. PAKIS NO.</t>
+  </si>
+  <si>
+    <t>BERSHKA KOTA KASABLANKA</t>
+  </si>
+  <si>
+    <t>BERSHKA</t>
+  </si>
+  <si>
+    <t>80555700_CT08PROBERSHKA24JAN2026PMTQ4887</t>
+  </si>
+  <si>
+    <t>JL. RAYA CASABLANCA NO.88, RT.2/RW.14, MENTENG DALAM, TEBET, JAKARTA, JAKARTA 12870</t>
+  </si>
+  <si>
+    <t>12:52</t>
+  </si>
+  <si>
+    <t>NIA</t>
+  </si>
+  <si>
+    <t>62 81284296162</t>
+  </si>
+  <si>
+    <t>80555700</t>
+  </si>
+  <si>
+    <t>BERSHKA SAINT MORITZ</t>
+  </si>
+  <si>
+    <t>80555700_CT08PROBERSHKA24JAN20266M2S5734</t>
+  </si>
+  <si>
+    <t>BERSKHA - SAINT MORIZT( LT.UG , DEPAN PULL AND BEAR) JL. PURI INDAH RAYA BLOCK U1, LANTAI UG 85-86, 111610 JAKARTA BARAT</t>
+  </si>
+  <si>
+    <t>ADI</t>
+  </si>
+  <si>
+    <t>87823289747</t>
+  </si>
+  <si>
+    <t>PAK KANTO PICKUP SEBELUM JAM 13</t>
+  </si>
+  <si>
+    <t>RPX</t>
+  </si>
+  <si>
+    <t>CLG20300</t>
+  </si>
+  <si>
+    <t>80615600_CT08PRORPX24JAN20260RJ56819</t>
+  </si>
+  <si>
+    <t>SERANG TRADE CENTER S25-26 JL RAYA SERANG KM 03 CV FAMILY AMANAH TRANSINDO (FAT BERSAUDARA) ATTN PAK KANTO</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>VAN</t>
+  </si>
+  <si>
+    <t>KANTO</t>
+  </si>
+  <si>
+    <t>0254 7913530</t>
+  </si>
+  <si>
+    <t>80615600</t>
+  </si>
+  <si>
+    <t>WILLYNOF JACK</t>
+  </si>
+  <si>
+    <t>ATMOS</t>
+  </si>
+  <si>
+    <t>BKI10047</t>
+  </si>
+  <si>
+    <t>81472100_CT08PROATMOS24JAN20262KQV5852</t>
+  </si>
+  <si>
+    <t>KOMPLEK JATIBENING ESTATE, JL. PIPIT II BLOK F6 NO 19 KEC. PONDOK GEDE, KEL. JATIBENING KOTA BEKASI</t>
+  </si>
+  <si>
+    <t>62 81313795075</t>
+  </si>
+  <si>
+    <t>ASURANSI + 2,800,000</t>
+  </si>
+  <si>
+    <t>ATMOS ONLINE INDONESIA ALAMAT : JL. ALAYDRUS NO.19RT.9/RW.7,</t>
+  </si>
+  <si>
+    <t>81472100</t>
+  </si>
+  <si>
+    <t>MELISSA CLUBE PALEMBANG ICON MALL PALEMBANG</t>
+  </si>
+  <si>
+    <t>81472000_CT08PROSEMBILANOHM24JAN20264V6D4319</t>
+  </si>
+  <si>
+    <t>MELISSA CLUBE PALEMBANG ICON MALL PALEMBANG ICON - G-30 JALAN POM IX (JALAN ANGKATAN 45) PALEMBANG, SOUTH SUMATERA, INDONESIA</t>
+  </si>
+  <si>
+    <t>DELLA</t>
+  </si>
+  <si>
+    <t>62 81274039385</t>
+  </si>
+  <si>
+    <t>ASURANSI + 900.000</t>
+  </si>
+  <si>
+    <t>ADYA ALAMAT EMAIL : ADYAIRZANTI20@GMAIL.COM ALAMAT LENGKAP :</t>
+  </si>
+  <si>
+    <t>TOKO ZAXY KOTA KASABLANKA</t>
+  </si>
+  <si>
+    <t>81472000_CT08PROSEMBILANOHM24JAN2026A8GF6472</t>
+  </si>
+  <si>
+    <t>KOTA KASABLANKA, 1ST FLOOR JL. RAYA CASABLANCA NO.88 1ST FLOOR, RT.16/RW.5, MENTENG DALAM, KEC. TEBET, KOTA JAKARTA SELATAN, DAERAH KHUSUS IBUKOTA JAKARTA 12870</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>62 85881727654</t>
+  </si>
+  <si>
+    <t>ASURANSI + 599,900</t>
+  </si>
+  <si>
+    <t>YUNI FITRIA ARIANTI JELLYDREAMS - #38019 NO.20 RT 02/ RW 11,</t>
+  </si>
+  <si>
+    <t>ATMOS PLAZA SENAYAN</t>
+  </si>
+  <si>
+    <t>81472100_CT08PROATMOS24JAN2026XF828391</t>
+  </si>
+  <si>
+    <t>‪‪‪ATMOS PLAZA SENAYAN PLAZA SENAYAN, JL. ASIA AFRIKA NO.8, RT.1/RW.3, GELORA, KOTA JAKARTA PUSAT</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>SUCI</t>
+  </si>
+  <si>
+    <t>62 85885932986</t>
+  </si>
+  <si>
+    <t>ASURANSI + IDR 2.899.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DICKY RAHADIAN ALAMAT LENGKAP : PT. ASURANSI MSIG INDONESIA </t>
+  </si>
+  <si>
+    <t>TOKO MELISSA TRANS STUDIO MALL CIBUBUR</t>
+  </si>
+  <si>
+    <t>DPK000</t>
+  </si>
+  <si>
+    <t>DPK10000</t>
+  </si>
+  <si>
+    <t>81472000_CT08PROSEMBILANOHM24JAN20261J8V5397</t>
+  </si>
+  <si>
+    <t>TRANS STUDIO MALL CIBUBUR - TOKO MELISSA LANTAI GF JL. ALTERNATIF CIBUBUR NO.230, HARJAMUKTI, CIMANGGIS, KOTA DEPOK, JAWA BARAT 16454 NO TELP PIC : +62 812-1094-0038</t>
+  </si>
+  <si>
+    <t>NINA</t>
+  </si>
+  <si>
+    <t>085860975424</t>
+  </si>
+  <si>
+    <t>ASURANSI + 1,000,000</t>
+  </si>
+  <si>
+    <t>CAHYA KAMILA ALAMAT EMAIL :  CAHKAMILA30@GMAIL.COM  ALAMAT L</t>
+  </si>
+  <si>
+    <t>STRADIVARIUS KOTA KASABLANKA</t>
+  </si>
+  <si>
+    <t>STRADIVARIUS</t>
+  </si>
+  <si>
+    <t>80556200_CT08PROSTRADIVARIUS24JAN2026ZJP31280</t>
+  </si>
+  <si>
+    <t>MALL KOTA KASABLANKA GROUND FLOOR UNIT 38 - 39 JLN. CASABLANCA NO.KAV 88 , RT.2/RW.14  MENTENG DALAM , JAKARTA SELATAN KODE POS : 12870 PHONE : 021-29465205</t>
+  </si>
+  <si>
+    <t>FAUZI</t>
+  </si>
+  <si>
+    <t>62 81285229028</t>
+  </si>
+  <si>
+    <t>80556200</t>
+  </si>
+  <si>
+    <t>MELISSA CLUBE PLAZA SENAYAN</t>
+  </si>
+  <si>
+    <t>81472000_CT08PROSEMBILANOHM24JAN2026YRQ19773</t>
+  </si>
+  <si>
+    <t>MELISSA CLUBE PLAZA SENAYAN PLAZA SENAYAN, L2#205B(1), 206A(1), 206A(2), 208A, &amp; 210A(1) JL. ASIA AFRIKA NO.8, RW.3, GELORA, KECAMATAN TANAH ABANG, KOTA JAKARTA PUSAT, DAERAH KHUSUS IBUKOTA JAKARTA 10270</t>
+  </si>
+  <si>
+    <t>ANGGINA</t>
+  </si>
+  <si>
+    <t>62 88210532542</t>
+  </si>
+  <si>
+    <t>ASURANSI + 1.550.000</t>
+  </si>
+  <si>
+    <t>ALBI FAUZY WARUNG NASI LOTEK BU OOM, JL. CICUKANG NO. 45 ARC</t>
+  </si>
+  <si>
+    <t>STRADIVARIUS CENTRAL PARK MALL</t>
+  </si>
+  <si>
+    <t>80556200_CT08PROSTRADIVARIUS24JAN2026NIKW2873</t>
+  </si>
+  <si>
+    <t>MALL CENTRAL PARK LT GF.JL LETJEN S PARMAN NO.28, TANJUNG DUREN. JAKARTA BARAT</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>VIANA</t>
+  </si>
+  <si>
+    <t>08811941947</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> + -</t>
+  </si>
+  <si>
+    <t>STRADIVARIUS GRAND INDONESIA</t>
+  </si>
+  <si>
+    <t>80556200_CT08PROSTRADIVARIUS24JAN20266MO82310</t>
+  </si>
+  <si>
+    <t>MALL GRAND INDONESIA LT1 SKYBRIDGE UNIT SB 12A-12B &amp; 15-16 &amp; JL. MH THAMRIN, NO 1 JAKARTA PUSAT 10310</t>
+  </si>
+  <si>
+    <t>13:01</t>
+  </si>
+  <si>
+    <t>MAHES</t>
+  </si>
+  <si>
+    <t>081232269442</t>
+  </si>
+  <si>
+    <t>WAJIB SCAN AWB PADA MILE + -</t>
+  </si>
+  <si>
+    <t>STRADIVARIUS PONDOK INDAH MALL 1</t>
+  </si>
+  <si>
+    <t>80556200_CT08PROSTRADIVARIUS24JAN20267ZI84150</t>
+  </si>
+  <si>
+    <t>PONDOK INDAH MALL 1 JL. METRO PONDOK INDAH KAV.IV, RT 1/RW 16 PD.PINANG. JAKARTA SELATAN</t>
+  </si>
+  <si>
+    <t>DHINI</t>
+  </si>
+  <si>
+    <t>087867006593</t>
+  </si>
+  <si>
+    <t>MCD KAREBOSI MAKASSAR</t>
+  </si>
+  <si>
+    <t>80024017_CT08PROREKSO24JAN2026YCIW0523</t>
+  </si>
+  <si>
+    <t>MCDONALD’S KAREBOSI #359 JL. A. AHMMAD YANI MAKASSAR</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>085340879608</t>
+  </si>
+  <si>
+    <t>80024017</t>
+  </si>
+  <si>
+    <t>SABILA (PIC POP UP STORE BALI)</t>
+  </si>
+  <si>
+    <t>81472000_CT08PROSEMBILANOHM24JAN20264M580068</t>
+  </si>
+  <si>
+    <t>TOKO ON  SHORE AMORA PERERENAN BALI,  JL. PANTAI PERERENAN, PERERENAN, KEC. MENGWI, KABUPATEN BADUNG, BALI - 80351</t>
+  </si>
+  <si>
+    <t>13:47</t>
+  </si>
+  <si>
+    <t>9 OHM</t>
+  </si>
+  <si>
+    <t>62 85891589374</t>
+  </si>
+  <si>
+    <t>ASURANSI + 2.700.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIVIA ALAMAT EMAIL : LIVIAWINDIANA@GMAIL.COM ALAMAT LENGKAP </t>
+  </si>
+  <si>
+    <t>ZARA ST MORITZ</t>
+  </si>
+  <si>
+    <t>80536501_CT08PROZARA24JAN20265EU78546</t>
+  </si>
+  <si>
+    <t>JL. PURI INDAH RAYA NO.1, RT.3/RW.2, KEMBANGAN SEL., KEC. KEMBANGAN, KOTA JAKARTA BARAT, DAERAH KHUSUS IBUKOTA JAKARTA 11610</t>
+  </si>
+  <si>
+    <t>MR AHMAD</t>
+  </si>
+  <si>
+    <t>62 82147444717</t>
+  </si>
+  <si>
+    <t>PULL&amp;BEAR ST MORITZ</t>
+  </si>
+  <si>
+    <t>80556101_CT08PROPULL&amp;BEAR24JAN2026ATIX4641</t>
+  </si>
+  <si>
+    <t>JL. PURI INDAH RAYA BLOK U1 , LANTAI UG 85-86 1, DAERAH KHUSUS IBUKOTA JAKARTA 11610 JAKARTA BARAT</t>
+  </si>
+  <si>
+    <t>ADIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- + - + </t>
+  </si>
+  <si>
+    <t>BUTTONSCARVES TSM CIBUBUR</t>
+  </si>
+  <si>
+    <t>80890503_CT08PROBUTTONSCARVESPICKUPOFFLINE24JAN2026T4SH4265</t>
+  </si>
+  <si>
+    <t>BUTTONSCARVES MALL TSM CIBUBUR LANTAI 1 , CIMANGGIS</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
+    <t>VELLA</t>
+  </si>
+  <si>
+    <t>081377008559</t>
+  </si>
+  <si>
+    <t>1. HELEN K SURAJAYA (085228071928) VILLA BUNDA 3 BLOK D NO 1</t>
+  </si>
+  <si>
+    <t>STORE NADA PUSPITA SENAYAN CITY</t>
+  </si>
+  <si>
+    <t>80887303_CT08PROBUTTONSCARVESPICKUPOFFLINE24JAN202685HH1081</t>
+  </si>
+  <si>
+    <t>STORE NADA PUSPITA SENCY LT.2, 2ND FLOOR UNIT 218-220 SENAYAN CITY MALL JL. ASIA AFRIKA NO.19 JAKARTA PUSAT</t>
+  </si>
+  <si>
+    <t>SILVI</t>
+  </si>
+  <si>
+    <t>081573902726</t>
+  </si>
+  <si>
+    <t>ISMA KOMPLEK DUTA REGENCY BLOK E NO.33A CIHANJUANG CIMAHI UT</t>
+  </si>
+  <si>
+    <t>BUTTONSCARVES PEJATEN</t>
+  </si>
+  <si>
+    <t>80890503_CT08PROBUTTONSCARVESPICKUPOFFLINE24JAN2026UD2C0770</t>
+  </si>
+  <si>
+    <t>BUTTONSCARVES JL. PEJATEN BARAT RAYA NO.6 1, RT.1/RW.8, PEJATEN BAR., PS. MINGGU, KOTA JAKARTA SELATAN, DAERAH KHUSUS IBUKOTA JAKARTA 12510</t>
+  </si>
+  <si>
+    <t>OKTA</t>
+  </si>
+  <si>
+    <t>08960182418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUATKAN AWB MANUAL - + + </t>
+  </si>
+  <si>
+    <t>1. PUTRI / HENGKY  ALAMAT : SHOJILAND BLOK CF-06 KEC : CANDI</t>
+  </si>
+  <si>
+    <t>ALEXANDER FIRMANSYAH WATU</t>
+  </si>
+  <si>
+    <t>XIAOMI TECHNOLOGY INDONESIA PT</t>
+  </si>
+  <si>
+    <t>LBJ000</t>
+  </si>
+  <si>
+    <t>LBJ10000</t>
+  </si>
+  <si>
+    <t>80521001_CT08PROXIAOMITECHNOLOGYINDONESIAPT24JAN2026GAH31073</t>
+  </si>
+  <si>
+    <t>JLRUTENG BENTENG JAWA NO 14 KELURAHAN COMPANG CAREP KECAMATAN LANGKE REMBONG KABUPATEN MANGGARAI PROVINSI NUSA TENGGARA TIMUR 86519 CAREP 86519 BORONG,KAB.MANGGARA 86519 JTBNN</t>
+  </si>
+  <si>
+    <t>6281236423245</t>
+  </si>
+  <si>
+    <t>CSS6901054796299</t>
+  </si>
+  <si>
+    <t>80521001</t>
+  </si>
+  <si>
+    <t>SAIRA RAMADANI</t>
+  </si>
+  <si>
+    <t>TKG000</t>
+  </si>
+  <si>
+    <t>TKG20400</t>
+  </si>
+  <si>
+    <t>80521001_CT08PROXIAOMITECHNOLOGYINDONESIAPT24JAN2026O3W20406</t>
+  </si>
+  <si>
+    <t>JL AIR HITAM RTRW 0903 DESA SEMARANG JAYA KEC AIR HITAM KAB LAMPUNG BARAT PROV LAMPUNG RUMAH PADE GAUL AIR HITAM DEPAN TOWER PERTAMA DARI ARAH PAJAR BULAN SEMARANG JAYA 34876 LIWA, LAMPUNG BARAT 34875 SUMATERA SELATAN</t>
+  </si>
+  <si>
+    <t>6281910240976</t>
+  </si>
+  <si>
+    <t>CSS1801055364254</t>
+  </si>
+  <si>
+    <t>ZARA CENTRAL PARK</t>
+  </si>
+  <si>
+    <t>80536501_CT08PROZARA24JAN2026LMRV4287</t>
+  </si>
+  <si>
+    <t>JL. LETJEN S. PARMAN NO.28, RT.12/RW.6, TJ. DUREN SEL., KEC. GROGOL PETAMBURAN, KOTA JAKARTA BARAT, DAERAH KHUSUS IBUKOTA JAKARTA 11470</t>
+  </si>
+  <si>
+    <t>13:59</t>
+  </si>
+  <si>
+    <t>FERDI</t>
+  </si>
+  <si>
+    <t>62 87784418504</t>
+  </si>
+  <si>
+    <t>TOKO MELISSA SUMMARECON EMERALD</t>
+  </si>
+  <si>
+    <t>KRW000</t>
+  </si>
+  <si>
+    <t>KRW10000</t>
+  </si>
+  <si>
+    <t>81472000_CT08PROSEMBILANOHM24JAN2026ZWZU2730</t>
+  </si>
+  <si>
+    <t>SUMMARECON VILLAGIO EMERALD, TOKO MELISSA  JL BULEVAR BLK A, NO KV 1. KONDANG JAYA, KEC KARAWANG TIMUR JAWA BARAT 41371</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>IKA LOVIKA</t>
+  </si>
+  <si>
+    <t>081389708436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASURANSI + </t>
+  </si>
+  <si>
+    <t>DESSIANA RATIH CITRA GRAN CLUSTER CLOVER GARDEN CC 18/1 JATI</t>
+  </si>
+  <si>
+    <t>POPUP STANLEY PASKAL</t>
+  </si>
+  <si>
+    <t>BDO10041</t>
+  </si>
+  <si>
+    <t>81472000_CT08PROSEMBILANOHM24JAN20269BP39515</t>
+  </si>
+  <si>
+    <t>POPUP STANLEY PASKAL PASKAL 23 LANTAI 1 JALAN PASIRKALIKI NO 25-27  KELURAHAN KEBON JERUK, KECAMATAN ANDIR, KOTA BANDUNG 40241</t>
+  </si>
+  <si>
+    <t>SHALLY</t>
+  </si>
+  <si>
+    <t>62 89659754005</t>
+  </si>
+  <si>
+    <t>ASURANSI + 710,000</t>
+  </si>
+  <si>
+    <t>SUSAN KRISBIANTO PERGUDANGAN MASPION INDUSTRI RAYA NO 22 SPP</t>
+  </si>
+  <si>
+    <t>BUTTONSCARVES BANDUNG</t>
+  </si>
+  <si>
+    <t>80890503_CT08PROBUTTONSCARVESPICKUPOFFLINE24JAN2026H6IA0511</t>
+  </si>
+  <si>
+    <t>14:26</t>
+  </si>
+  <si>
+    <t>H. MUSLIM MUBAROK, PONDOK PESANTREN AL-MAJIDIYAH DS. MEKARSA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -105,7 +1836,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,11 +2169,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U1"/>
-  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U12"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="45.140625" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
     <col min="2" max="2" width="31.28515625" customWidth="1"/>
     <col min="3" max="3" width="16.140625" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" customWidth="1"/>
@@ -517,8 +2248,5108 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>34</v>
+      </c>
+      <c r="R4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>34</v>
+      </c>
+      <c r="R5" t="s">
+        <v>35</v>
+      </c>
+      <c r="S5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>34</v>
+      </c>
+      <c r="R6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" t="s">
+        <v>23</v>
+      </c>
+      <c r="U6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>34</v>
+      </c>
+      <c r="R7" t="s">
+        <v>35</v>
+      </c>
+      <c r="S7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" t="s">
+        <v>23</v>
+      </c>
+      <c r="U7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
+        <v>47</v>
+      </c>
+      <c r="N8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>34</v>
+      </c>
+      <c r="R8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" t="s">
+        <v>23</v>
+      </c>
+      <c r="U8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>34</v>
+      </c>
+      <c r="R9" t="s">
+        <v>35</v>
+      </c>
+      <c r="S9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" t="s">
+        <v>23</v>
+      </c>
+      <c r="U9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>58</v>
+      </c>
+      <c r="R10" t="s">
+        <v>59</v>
+      </c>
+      <c r="S10" t="s">
+        <v>60</v>
+      </c>
+      <c r="T10" t="s">
+        <v>23</v>
+      </c>
+      <c r="U10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" t="s">
+        <v>68</v>
+      </c>
+      <c r="N11" t="s">
+        <v>69</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>70</v>
+      </c>
+      <c r="R11" t="s">
+        <v>71</v>
+      </c>
+      <c r="S11" t="s">
+        <v>72</v>
+      </c>
+      <c r="T11" t="s">
+        <v>23</v>
+      </c>
+      <c r="U11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" t="s">
+        <v>79</v>
+      </c>
+      <c r="L12" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" t="s">
+        <v>80</v>
+      </c>
+      <c r="N12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>82</v>
+      </c>
+      <c r="R12" t="s">
+        <v>59</v>
+      </c>
+      <c r="S12" t="s">
+        <v>23</v>
+      </c>
+      <c r="T12" t="s">
+        <v>23</v>
+      </c>
+      <c r="U12" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U74"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R2" t="s">
+        <v>94</v>
+      </c>
+      <c r="S2" t="s">
+        <v>95</v>
+      </c>
+      <c r="T2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>105</v>
+      </c>
+      <c r="R3" t="s">
+        <v>106</v>
+      </c>
+      <c r="S3" t="s">
+        <v>107</v>
+      </c>
+      <c r="T3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M4" t="s">
+        <v>114</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>116</v>
+      </c>
+      <c r="R4" t="s">
+        <v>117</v>
+      </c>
+      <c r="S4" t="s">
+        <v>118</v>
+      </c>
+      <c r="T4" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" t="s">
+        <v>123</v>
+      </c>
+      <c r="L5" t="s">
+        <v>90</v>
+      </c>
+      <c r="M5" t="s">
+        <v>124</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>126</v>
+      </c>
+      <c r="R5" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" t="s">
+        <v>127</v>
+      </c>
+      <c r="T5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>131</v>
+      </c>
+      <c r="K6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M6" t="s">
+        <v>133</v>
+      </c>
+      <c r="N6" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>135</v>
+      </c>
+      <c r="R6" t="s">
+        <v>136</v>
+      </c>
+      <c r="S6" t="s">
+        <v>137</v>
+      </c>
+      <c r="T6" t="s">
+        <v>23</v>
+      </c>
+      <c r="U6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s">
+        <v>141</v>
+      </c>
+      <c r="K7" t="s">
+        <v>142</v>
+      </c>
+      <c r="L7" t="s">
+        <v>90</v>
+      </c>
+      <c r="M7" t="s">
+        <v>133</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>144</v>
+      </c>
+      <c r="R7" t="s">
+        <v>35</v>
+      </c>
+      <c r="S7" t="s">
+        <v>145</v>
+      </c>
+      <c r="T7" t="s">
+        <v>23</v>
+      </c>
+      <c r="U7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s">
+        <v>150</v>
+      </c>
+      <c r="K8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M8" t="s">
+        <v>152</v>
+      </c>
+      <c r="N8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>154</v>
+      </c>
+      <c r="R8" t="s">
+        <v>155</v>
+      </c>
+      <c r="S8" t="s">
+        <v>156</v>
+      </c>
+      <c r="T8" t="s">
+        <v>23</v>
+      </c>
+      <c r="U8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>158</v>
+      </c>
+      <c r="G9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" t="s">
+        <v>160</v>
+      </c>
+      <c r="K9" t="s">
+        <v>161</v>
+      </c>
+      <c r="L9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9" t="s">
+        <v>152</v>
+      </c>
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>163</v>
+      </c>
+      <c r="R9" t="s">
+        <v>164</v>
+      </c>
+      <c r="S9" t="s">
+        <v>118</v>
+      </c>
+      <c r="T9" t="s">
+        <v>23</v>
+      </c>
+      <c r="U9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>168</v>
+      </c>
+      <c r="K10" t="s">
+        <v>169</v>
+      </c>
+      <c r="L10" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" t="s">
+        <v>170</v>
+      </c>
+      <c r="N10" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>172</v>
+      </c>
+      <c r="R10" t="s">
+        <v>173</v>
+      </c>
+      <c r="S10" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" t="s">
+        <v>23</v>
+      </c>
+      <c r="U10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>177</v>
+      </c>
+      <c r="J11" t="s">
+        <v>178</v>
+      </c>
+      <c r="K11" t="s">
+        <v>179</v>
+      </c>
+      <c r="L11" t="s">
+        <v>90</v>
+      </c>
+      <c r="M11" t="s">
+        <v>170</v>
+      </c>
+      <c r="N11" t="s">
+        <v>177</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>23</v>
+      </c>
+      <c r="R11" t="s">
+        <v>59</v>
+      </c>
+      <c r="S11" t="s">
+        <v>23</v>
+      </c>
+      <c r="U11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>182</v>
+      </c>
+      <c r="G12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" t="s">
+        <v>184</v>
+      </c>
+      <c r="J12" t="s">
+        <v>185</v>
+      </c>
+      <c r="K12" t="s">
+        <v>186</v>
+      </c>
+      <c r="L12" t="s">
+        <v>90</v>
+      </c>
+      <c r="M12" t="s">
+        <v>170</v>
+      </c>
+      <c r="N12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>188</v>
+      </c>
+      <c r="R12" t="s">
+        <v>189</v>
+      </c>
+      <c r="S12" t="s">
+        <v>23</v>
+      </c>
+      <c r="U12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" t="s">
+        <v>184</v>
+      </c>
+      <c r="J13" t="s">
+        <v>193</v>
+      </c>
+      <c r="K13" t="s">
+        <v>194</v>
+      </c>
+      <c r="L13" t="s">
+        <v>90</v>
+      </c>
+      <c r="M13" t="s">
+        <v>170</v>
+      </c>
+      <c r="N13" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>195</v>
+      </c>
+      <c r="R13" t="s">
+        <v>189</v>
+      </c>
+      <c r="S13" t="s">
+        <v>196</v>
+      </c>
+      <c r="U13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" t="s">
+        <v>177</v>
+      </c>
+      <c r="J14" t="s">
+        <v>198</v>
+      </c>
+      <c r="K14" t="s">
+        <v>199</v>
+      </c>
+      <c r="L14" t="s">
+        <v>90</v>
+      </c>
+      <c r="M14" t="s">
+        <v>170</v>
+      </c>
+      <c r="N14" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>201</v>
+      </c>
+      <c r="R14" t="s">
+        <v>189</v>
+      </c>
+      <c r="S14" t="s">
+        <v>202</v>
+      </c>
+      <c r="U14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>203</v>
+      </c>
+      <c r="B15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>191</v>
+      </c>
+      <c r="G15" t="s">
+        <v>192</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" t="s">
+        <v>204</v>
+      </c>
+      <c r="J15" t="s">
+        <v>205</v>
+      </c>
+      <c r="K15" t="s">
+        <v>206</v>
+      </c>
+      <c r="L15" t="s">
+        <v>90</v>
+      </c>
+      <c r="M15" t="s">
+        <v>207</v>
+      </c>
+      <c r="N15" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>209</v>
+      </c>
+      <c r="R15" t="s">
+        <v>189</v>
+      </c>
+      <c r="S15" t="s">
+        <v>210</v>
+      </c>
+      <c r="U15" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" t="s">
+        <v>213</v>
+      </c>
+      <c r="K16" t="s">
+        <v>214</v>
+      </c>
+      <c r="L16" t="s">
+        <v>90</v>
+      </c>
+      <c r="M16" t="s">
+        <v>207</v>
+      </c>
+      <c r="N16" t="s">
+        <v>69</v>
+      </c>
+      <c r="O16" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>216</v>
+      </c>
+      <c r="R16" t="s">
+        <v>217</v>
+      </c>
+      <c r="S16" t="s">
+        <v>125</v>
+      </c>
+      <c r="T16" t="s">
+        <v>23</v>
+      </c>
+      <c r="U16" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" t="s">
+        <v>221</v>
+      </c>
+      <c r="K18" t="s">
+        <v>222</v>
+      </c>
+      <c r="L18" t="s">
+        <v>90</v>
+      </c>
+      <c r="M18" t="s">
+        <v>223</v>
+      </c>
+      <c r="N18" t="s">
+        <v>31</v>
+      </c>
+      <c r="O18" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>225</v>
+      </c>
+      <c r="R18" t="s">
+        <v>226</v>
+      </c>
+      <c r="S18" t="s">
+        <v>227</v>
+      </c>
+      <c r="T18" t="s">
+        <v>23</v>
+      </c>
+      <c r="U18" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" t="s">
+        <v>230</v>
+      </c>
+      <c r="F19" t="s">
+        <v>231</v>
+      </c>
+      <c r="G19" t="s">
+        <v>232</v>
+      </c>
+      <c r="I19" t="s">
+        <v>233</v>
+      </c>
+      <c r="J19" t="s">
+        <v>234</v>
+      </c>
+      <c r="K19" t="s">
+        <v>235</v>
+      </c>
+      <c r="L19" t="s">
+        <v>90</v>
+      </c>
+      <c r="M19" t="s">
+        <v>236</v>
+      </c>
+      <c r="N19" t="s">
+        <v>237</v>
+      </c>
+      <c r="O19" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q19">
+        <v>85966247575</v>
+      </c>
+      <c r="R19" t="s">
+        <v>238</v>
+      </c>
+      <c r="S19" t="s">
+        <v>239</v>
+      </c>
+      <c r="T19" t="s">
+        <v>125</v>
+      </c>
+      <c r="U19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>241</v>
+      </c>
+      <c r="B20" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" t="s">
+        <v>243</v>
+      </c>
+      <c r="J20" t="s">
+        <v>244</v>
+      </c>
+      <c r="K20" t="s">
+        <v>245</v>
+      </c>
+      <c r="L20" t="s">
+        <v>90</v>
+      </c>
+      <c r="M20" t="s">
+        <v>246</v>
+      </c>
+      <c r="N20" t="s">
+        <v>31</v>
+      </c>
+      <c r="O20" t="s">
+        <v>32</v>
+      </c>
+      <c r="P20" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>248</v>
+      </c>
+      <c r="R20" t="s">
+        <v>249</v>
+      </c>
+      <c r="S20" t="s">
+        <v>23</v>
+      </c>
+      <c r="U20" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B21" t="s">
+        <v>212</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" t="s">
+        <v>252</v>
+      </c>
+      <c r="K21" t="s">
+        <v>253</v>
+      </c>
+      <c r="L21" t="s">
+        <v>90</v>
+      </c>
+      <c r="M21" t="s">
+        <v>246</v>
+      </c>
+      <c r="N21" t="s">
+        <v>69</v>
+      </c>
+      <c r="O21" t="s">
+        <v>32</v>
+      </c>
+      <c r="P21" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>255</v>
+      </c>
+      <c r="R21" t="s">
+        <v>256</v>
+      </c>
+      <c r="S21" t="s">
+        <v>125</v>
+      </c>
+      <c r="T21" t="s">
+        <v>23</v>
+      </c>
+      <c r="U21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>257</v>
+      </c>
+      <c r="B22" t="s">
+        <v>258</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" t="s">
+        <v>259</v>
+      </c>
+      <c r="K22" t="s">
+        <v>260</v>
+      </c>
+      <c r="L22" t="s">
+        <v>90</v>
+      </c>
+      <c r="M22" t="s">
+        <v>261</v>
+      </c>
+      <c r="N22" t="s">
+        <v>31</v>
+      </c>
+      <c r="O22" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>263</v>
+      </c>
+      <c r="R22" t="s">
+        <v>264</v>
+      </c>
+      <c r="S22" t="s">
+        <v>265</v>
+      </c>
+      <c r="T22" t="s">
+        <v>23</v>
+      </c>
+      <c r="U22" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="23" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" t="s">
+        <v>212</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" t="s">
+        <v>268</v>
+      </c>
+      <c r="K23" t="s">
+        <v>269</v>
+      </c>
+      <c r="L23" t="s">
+        <v>90</v>
+      </c>
+      <c r="M23" t="s">
+        <v>261</v>
+      </c>
+      <c r="N23" t="s">
+        <v>69</v>
+      </c>
+      <c r="O23" t="s">
+        <v>32</v>
+      </c>
+      <c r="P23" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>271</v>
+      </c>
+      <c r="R23" t="s">
+        <v>256</v>
+      </c>
+      <c r="S23" t="s">
+        <v>125</v>
+      </c>
+      <c r="T23" t="s">
+        <v>23</v>
+      </c>
+      <c r="U23" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>272</v>
+      </c>
+      <c r="B24" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" t="s">
+        <v>273</v>
+      </c>
+      <c r="K24" t="s">
+        <v>274</v>
+      </c>
+      <c r="L24" t="s">
+        <v>90</v>
+      </c>
+      <c r="M24" t="s">
+        <v>275</v>
+      </c>
+      <c r="N24" t="s">
+        <v>69</v>
+      </c>
+      <c r="O24" t="s">
+        <v>32</v>
+      </c>
+      <c r="P24" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>277</v>
+      </c>
+      <c r="R24" t="s">
+        <v>278</v>
+      </c>
+      <c r="S24" t="s">
+        <v>279</v>
+      </c>
+      <c r="T24" t="s">
+        <v>23</v>
+      </c>
+      <c r="U24" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="25" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>280</v>
+      </c>
+      <c r="B25" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" t="s">
+        <v>184</v>
+      </c>
+      <c r="J25" t="s">
+        <v>281</v>
+      </c>
+      <c r="K25" t="s">
+        <v>282</v>
+      </c>
+      <c r="L25" t="s">
+        <v>90</v>
+      </c>
+      <c r="M25" t="s">
+        <v>283</v>
+      </c>
+      <c r="N25" t="s">
+        <v>31</v>
+      </c>
+      <c r="O25" t="s">
+        <v>32</v>
+      </c>
+      <c r="P25" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>285</v>
+      </c>
+      <c r="R25" t="s">
+        <v>189</v>
+      </c>
+      <c r="S25" t="s">
+        <v>286</v>
+      </c>
+      <c r="U25" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>287</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" t="s">
+        <v>288</v>
+      </c>
+      <c r="K26" t="s">
+        <v>289</v>
+      </c>
+      <c r="L26" t="s">
+        <v>90</v>
+      </c>
+      <c r="M26" t="s">
+        <v>283</v>
+      </c>
+      <c r="N26" t="s">
+        <v>31</v>
+      </c>
+      <c r="O26" t="s">
+        <v>32</v>
+      </c>
+      <c r="P26" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>291</v>
+      </c>
+      <c r="R26" t="s">
+        <v>217</v>
+      </c>
+      <c r="S26" t="s">
+        <v>292</v>
+      </c>
+      <c r="T26" t="s">
+        <v>23</v>
+      </c>
+      <c r="U26" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="27" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>294</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" t="s">
+        <v>295</v>
+      </c>
+      <c r="K27" t="s">
+        <v>296</v>
+      </c>
+      <c r="L27" t="s">
+        <v>90</v>
+      </c>
+      <c r="M27" t="s">
+        <v>283</v>
+      </c>
+      <c r="N27" t="s">
+        <v>31</v>
+      </c>
+      <c r="O27" t="s">
+        <v>32</v>
+      </c>
+      <c r="P27" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>298</v>
+      </c>
+      <c r="R27" t="s">
+        <v>299</v>
+      </c>
+      <c r="S27" t="s">
+        <v>300</v>
+      </c>
+      <c r="T27" t="s">
+        <v>23</v>
+      </c>
+      <c r="U27" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>294</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" t="s">
+        <v>302</v>
+      </c>
+      <c r="K28" t="s">
+        <v>296</v>
+      </c>
+      <c r="L28" t="s">
+        <v>90</v>
+      </c>
+      <c r="M28" t="s">
+        <v>283</v>
+      </c>
+      <c r="N28" t="s">
+        <v>31</v>
+      </c>
+      <c r="O28" t="s">
+        <v>32</v>
+      </c>
+      <c r="P28" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>298</v>
+      </c>
+      <c r="R28" t="s">
+        <v>299</v>
+      </c>
+      <c r="S28" t="s">
+        <v>303</v>
+      </c>
+      <c r="T28" t="s">
+        <v>23</v>
+      </c>
+      <c r="U28" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="29" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>304</v>
+      </c>
+      <c r="B29" t="s">
+        <v>212</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" t="s">
+        <v>305</v>
+      </c>
+      <c r="G29" t="s">
+        <v>306</v>
+      </c>
+      <c r="H29" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29" t="s">
+        <v>307</v>
+      </c>
+      <c r="K29" t="s">
+        <v>308</v>
+      </c>
+      <c r="L29" t="s">
+        <v>90</v>
+      </c>
+      <c r="M29" t="s">
+        <v>309</v>
+      </c>
+      <c r="N29" t="s">
+        <v>69</v>
+      </c>
+      <c r="O29" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>311</v>
+      </c>
+      <c r="R29" t="s">
+        <v>217</v>
+      </c>
+      <c r="S29" t="s">
+        <v>125</v>
+      </c>
+      <c r="T29" t="s">
+        <v>23</v>
+      </c>
+      <c r="U29" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="30" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>312</v>
+      </c>
+      <c r="B30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" t="s">
+        <v>313</v>
+      </c>
+      <c r="G30" t="s">
+        <v>314</v>
+      </c>
+      <c r="H30" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30" t="s">
+        <v>315</v>
+      </c>
+      <c r="K30" t="s">
+        <v>316</v>
+      </c>
+      <c r="L30" t="s">
+        <v>90</v>
+      </c>
+      <c r="M30" t="s">
+        <v>317</v>
+      </c>
+      <c r="N30" t="s">
+        <v>69</v>
+      </c>
+      <c r="O30" t="s">
+        <v>32</v>
+      </c>
+      <c r="P30" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>319</v>
+      </c>
+      <c r="R30" t="s">
+        <v>217</v>
+      </c>
+      <c r="S30" t="s">
+        <v>125</v>
+      </c>
+      <c r="T30" t="s">
+        <v>23</v>
+      </c>
+      <c r="U30" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="31" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>321</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31" t="s">
+        <v>322</v>
+      </c>
+      <c r="K31" t="s">
+        <v>323</v>
+      </c>
+      <c r="L31" t="s">
+        <v>90</v>
+      </c>
+      <c r="M31" t="s">
+        <v>317</v>
+      </c>
+      <c r="N31" t="s">
+        <v>31</v>
+      </c>
+      <c r="O31" t="s">
+        <v>32</v>
+      </c>
+      <c r="P31" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>324</v>
+      </c>
+      <c r="R31" t="s">
+        <v>217</v>
+      </c>
+      <c r="S31" t="s">
+        <v>23</v>
+      </c>
+      <c r="T31" t="s">
+        <v>23</v>
+      </c>
+      <c r="U31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>325</v>
+      </c>
+      <c r="B32" t="s">
+        <v>326</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" t="s">
+        <v>52</v>
+      </c>
+      <c r="J32" t="s">
+        <v>327</v>
+      </c>
+      <c r="K32" t="s">
+        <v>328</v>
+      </c>
+      <c r="L32" t="s">
+        <v>90</v>
+      </c>
+      <c r="M32" t="s">
+        <v>317</v>
+      </c>
+      <c r="N32" t="s">
+        <v>31</v>
+      </c>
+      <c r="O32" t="s">
+        <v>32</v>
+      </c>
+      <c r="P32" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>330</v>
+      </c>
+      <c r="R32" t="s">
+        <v>59</v>
+      </c>
+      <c r="S32" t="s">
+        <v>331</v>
+      </c>
+      <c r="T32" t="s">
+        <v>23</v>
+      </c>
+      <c r="U32" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="34" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>333</v>
+      </c>
+      <c r="B34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" t="s">
+        <v>334</v>
+      </c>
+      <c r="G34" t="s">
+        <v>335</v>
+      </c>
+      <c r="H34" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" t="s">
+        <v>336</v>
+      </c>
+      <c r="J34" t="s">
+        <v>337</v>
+      </c>
+      <c r="K34" t="s">
+        <v>338</v>
+      </c>
+      <c r="L34" t="s">
+        <v>90</v>
+      </c>
+      <c r="M34" t="s">
+        <v>339</v>
+      </c>
+      <c r="N34" t="s">
+        <v>31</v>
+      </c>
+      <c r="O34" t="s">
+        <v>32</v>
+      </c>
+      <c r="P34" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>341</v>
+      </c>
+      <c r="R34" t="s">
+        <v>299</v>
+      </c>
+      <c r="S34" t="s">
+        <v>342</v>
+      </c>
+      <c r="T34" t="s">
+        <v>23</v>
+      </c>
+      <c r="U34" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="35" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>343</v>
+      </c>
+      <c r="B35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" t="s">
+        <v>26</v>
+      </c>
+      <c r="J35" t="s">
+        <v>344</v>
+      </c>
+      <c r="K35" t="s">
+        <v>345</v>
+      </c>
+      <c r="L35" t="s">
+        <v>90</v>
+      </c>
+      <c r="M35" t="s">
+        <v>346</v>
+      </c>
+      <c r="N35" t="s">
+        <v>31</v>
+      </c>
+      <c r="O35" t="s">
+        <v>32</v>
+      </c>
+      <c r="P35" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>348</v>
+      </c>
+      <c r="R35" t="s">
+        <v>299</v>
+      </c>
+      <c r="S35" t="s">
+        <v>349</v>
+      </c>
+      <c r="T35" t="s">
+        <v>23</v>
+      </c>
+      <c r="U35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>350</v>
+      </c>
+      <c r="B36" t="s">
+        <v>326</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" t="s">
+        <v>191</v>
+      </c>
+      <c r="G36" t="s">
+        <v>351</v>
+      </c>
+      <c r="H36" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36" t="s">
+        <v>352</v>
+      </c>
+      <c r="K36" t="s">
+        <v>353</v>
+      </c>
+      <c r="L36" t="s">
+        <v>90</v>
+      </c>
+      <c r="M36" t="s">
+        <v>346</v>
+      </c>
+      <c r="N36" t="s">
+        <v>31</v>
+      </c>
+      <c r="O36" t="s">
+        <v>32</v>
+      </c>
+      <c r="P36" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>355</v>
+      </c>
+      <c r="R36" t="s">
+        <v>59</v>
+      </c>
+      <c r="S36" t="s">
+        <v>356</v>
+      </c>
+      <c r="T36" t="s">
+        <v>23</v>
+      </c>
+      <c r="U36" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="37" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>350</v>
+      </c>
+      <c r="B37" t="s">
+        <v>326</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" t="s">
+        <v>191</v>
+      </c>
+      <c r="G37" t="s">
+        <v>351</v>
+      </c>
+      <c r="H37" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" t="s">
+        <v>26</v>
+      </c>
+      <c r="J37" t="s">
+        <v>358</v>
+      </c>
+      <c r="K37" t="s">
+        <v>353</v>
+      </c>
+      <c r="L37" t="s">
+        <v>90</v>
+      </c>
+      <c r="M37" t="s">
+        <v>346</v>
+      </c>
+      <c r="N37" t="s">
+        <v>31</v>
+      </c>
+      <c r="O37" t="s">
+        <v>32</v>
+      </c>
+      <c r="P37" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>355</v>
+      </c>
+      <c r="R37" t="s">
+        <v>59</v>
+      </c>
+      <c r="S37" t="s">
+        <v>359</v>
+      </c>
+      <c r="T37" t="s">
+        <v>23</v>
+      </c>
+      <c r="U37" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="39" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>360</v>
+      </c>
+      <c r="B39" t="s">
+        <v>140</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" t="s">
+        <v>361</v>
+      </c>
+      <c r="G39" t="s">
+        <v>362</v>
+      </c>
+      <c r="H39" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" t="s">
+        <v>336</v>
+      </c>
+      <c r="J39" t="s">
+        <v>363</v>
+      </c>
+      <c r="K39" t="s">
+        <v>364</v>
+      </c>
+      <c r="L39" t="s">
+        <v>90</v>
+      </c>
+      <c r="M39" t="s">
+        <v>365</v>
+      </c>
+      <c r="N39" t="s">
+        <v>69</v>
+      </c>
+      <c r="O39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P39" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>23</v>
+      </c>
+      <c r="R39" t="s">
+        <v>367</v>
+      </c>
+      <c r="S39" t="s">
+        <v>368</v>
+      </c>
+      <c r="T39" t="s">
+        <v>23</v>
+      </c>
+      <c r="U39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>369</v>
+      </c>
+      <c r="B40" t="s">
+        <v>370</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" t="s">
+        <v>371</v>
+      </c>
+      <c r="G40" t="s">
+        <v>372</v>
+      </c>
+      <c r="H40" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" t="s">
+        <v>52</v>
+      </c>
+      <c r="J40" t="s">
+        <v>373</v>
+      </c>
+      <c r="K40" t="s">
+        <v>374</v>
+      </c>
+      <c r="L40" t="s">
+        <v>90</v>
+      </c>
+      <c r="M40" t="s">
+        <v>365</v>
+      </c>
+      <c r="N40" t="s">
+        <v>69</v>
+      </c>
+      <c r="O40" t="s">
+        <v>32</v>
+      </c>
+      <c r="P40" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>375</v>
+      </c>
+      <c r="R40" t="s">
+        <v>59</v>
+      </c>
+      <c r="S40" t="s">
+        <v>376</v>
+      </c>
+      <c r="T40" t="s">
+        <v>23</v>
+      </c>
+      <c r="U40" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="41" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>378</v>
+      </c>
+      <c r="B41" t="s">
+        <v>379</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" t="s">
+        <v>191</v>
+      </c>
+      <c r="G41" t="s">
+        <v>192</v>
+      </c>
+      <c r="H41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41" t="s">
+        <v>380</v>
+      </c>
+      <c r="K41" t="s">
+        <v>381</v>
+      </c>
+      <c r="L41" t="s">
+        <v>90</v>
+      </c>
+      <c r="M41" t="s">
+        <v>365</v>
+      </c>
+      <c r="N41" t="s">
+        <v>31</v>
+      </c>
+      <c r="O41" t="s">
+        <v>32</v>
+      </c>
+      <c r="P41" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>382</v>
+      </c>
+      <c r="R41" t="s">
+        <v>217</v>
+      </c>
+      <c r="S41" t="s">
+        <v>125</v>
+      </c>
+      <c r="T41" t="s">
+        <v>23</v>
+      </c>
+      <c r="U41" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="42" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>384</v>
+      </c>
+      <c r="B42" t="s">
+        <v>385</v>
+      </c>
+      <c r="C42" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" t="s">
+        <v>386</v>
+      </c>
+      <c r="G42" t="s">
+        <v>387</v>
+      </c>
+      <c r="H42" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" t="s">
+        <v>26</v>
+      </c>
+      <c r="J42" t="s">
+        <v>388</v>
+      </c>
+      <c r="K42" t="s">
+        <v>389</v>
+      </c>
+      <c r="L42" t="s">
+        <v>90</v>
+      </c>
+      <c r="M42" t="s">
+        <v>365</v>
+      </c>
+      <c r="N42" t="s">
+        <v>69</v>
+      </c>
+      <c r="O42" t="s">
+        <v>32</v>
+      </c>
+      <c r="P42" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>390</v>
+      </c>
+      <c r="R42" t="s">
+        <v>59</v>
+      </c>
+      <c r="S42" t="s">
+        <v>23</v>
+      </c>
+      <c r="U42" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="43" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>392</v>
+      </c>
+      <c r="B43" t="s">
+        <v>393</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" t="s">
+        <v>394</v>
+      </c>
+      <c r="G43" t="s">
+        <v>395</v>
+      </c>
+      <c r="H43" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" t="s">
+        <v>336</v>
+      </c>
+      <c r="J43" t="s">
+        <v>396</v>
+      </c>
+      <c r="K43" t="s">
+        <v>397</v>
+      </c>
+      <c r="L43" t="s">
+        <v>90</v>
+      </c>
+      <c r="M43" t="s">
+        <v>398</v>
+      </c>
+      <c r="N43" t="s">
+        <v>69</v>
+      </c>
+      <c r="O43" t="s">
+        <v>32</v>
+      </c>
+      <c r="P43" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>399</v>
+      </c>
+      <c r="R43" t="s">
+        <v>59</v>
+      </c>
+      <c r="S43" t="s">
+        <v>23</v>
+      </c>
+      <c r="U43" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="44" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>400</v>
+      </c>
+      <c r="B44" t="s">
+        <v>258</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" t="s">
+        <v>305</v>
+      </c>
+      <c r="G44" t="s">
+        <v>306</v>
+      </c>
+      <c r="H44" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44" t="s">
+        <v>401</v>
+      </c>
+      <c r="K44" t="s">
+        <v>402</v>
+      </c>
+      <c r="L44" t="s">
+        <v>90</v>
+      </c>
+      <c r="M44" t="s">
+        <v>398</v>
+      </c>
+      <c r="N44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O44" t="s">
+        <v>32</v>
+      </c>
+      <c r="P44" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>404</v>
+      </c>
+      <c r="R44" t="s">
+        <v>405</v>
+      </c>
+      <c r="S44" t="s">
+        <v>406</v>
+      </c>
+      <c r="T44" t="s">
+        <v>23</v>
+      </c>
+      <c r="U44" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="45" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>407</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" t="s">
+        <v>408</v>
+      </c>
+      <c r="G45" t="s">
+        <v>409</v>
+      </c>
+      <c r="H45" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" t="s">
+        <v>52</v>
+      </c>
+      <c r="J45" t="s">
+        <v>410</v>
+      </c>
+      <c r="K45" t="s">
+        <v>407</v>
+      </c>
+      <c r="L45" t="s">
+        <v>90</v>
+      </c>
+      <c r="M45" t="s">
+        <v>411</v>
+      </c>
+      <c r="N45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O45" t="s">
+        <v>32</v>
+      </c>
+      <c r="P45" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>413</v>
+      </c>
+      <c r="R45" t="s">
+        <v>299</v>
+      </c>
+      <c r="S45" t="s">
+        <v>414</v>
+      </c>
+      <c r="T45" t="s">
+        <v>23</v>
+      </c>
+      <c r="U45" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>415</v>
+      </c>
+      <c r="B47" t="s">
+        <v>416</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" t="s">
+        <v>25</v>
+      </c>
+      <c r="H47" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" t="s">
+        <v>26</v>
+      </c>
+      <c r="J47" t="s">
+        <v>417</v>
+      </c>
+      <c r="K47" t="s">
+        <v>418</v>
+      </c>
+      <c r="L47" t="s">
+        <v>90</v>
+      </c>
+      <c r="M47" t="s">
+        <v>419</v>
+      </c>
+      <c r="N47" t="s">
+        <v>69</v>
+      </c>
+      <c r="O47" t="s">
+        <v>32</v>
+      </c>
+      <c r="P47" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>421</v>
+      </c>
+      <c r="R47" t="s">
+        <v>217</v>
+      </c>
+      <c r="S47" t="s">
+        <v>125</v>
+      </c>
+      <c r="T47" t="s">
+        <v>23</v>
+      </c>
+      <c r="U47" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="48" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>423</v>
+      </c>
+      <c r="B48" t="s">
+        <v>416</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" t="s">
+        <v>25</v>
+      </c>
+      <c r="H48" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" t="s">
+        <v>26</v>
+      </c>
+      <c r="J48" t="s">
+        <v>424</v>
+      </c>
+      <c r="K48" t="s">
+        <v>425</v>
+      </c>
+      <c r="L48" t="s">
+        <v>90</v>
+      </c>
+      <c r="M48" t="s">
+        <v>419</v>
+      </c>
+      <c r="N48" t="s">
+        <v>69</v>
+      </c>
+      <c r="O48" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>427</v>
+      </c>
+      <c r="R48" t="s">
+        <v>256</v>
+      </c>
+      <c r="S48" t="s">
+        <v>125</v>
+      </c>
+      <c r="T48" t="s">
+        <v>23</v>
+      </c>
+      <c r="U48" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="49" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>428</v>
+      </c>
+      <c r="B49" t="s">
+        <v>429</v>
+      </c>
+      <c r="C49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49" t="s">
+        <v>386</v>
+      </c>
+      <c r="G49" t="s">
+        <v>430</v>
+      </c>
+      <c r="H49" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" t="s">
+        <v>26</v>
+      </c>
+      <c r="J49" t="s">
+        <v>431</v>
+      </c>
+      <c r="K49" t="s">
+        <v>432</v>
+      </c>
+      <c r="L49" t="s">
+        <v>90</v>
+      </c>
+      <c r="M49" t="s">
+        <v>433</v>
+      </c>
+      <c r="N49" t="s">
+        <v>434</v>
+      </c>
+      <c r="O49" t="s">
+        <v>32</v>
+      </c>
+      <c r="P49" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>436</v>
+      </c>
+      <c r="R49" t="s">
+        <v>59</v>
+      </c>
+      <c r="S49" t="s">
+        <v>23</v>
+      </c>
+      <c r="T49" t="s">
+        <v>23</v>
+      </c>
+      <c r="U49" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="50" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>438</v>
+      </c>
+      <c r="B50" t="s">
+        <v>439</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" t="s">
+        <v>182</v>
+      </c>
+      <c r="G50" t="s">
+        <v>440</v>
+      </c>
+      <c r="H50" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" t="s">
+        <v>26</v>
+      </c>
+      <c r="J50" t="s">
+        <v>441</v>
+      </c>
+      <c r="K50" t="s">
+        <v>442</v>
+      </c>
+      <c r="L50" t="s">
+        <v>90</v>
+      </c>
+      <c r="M50" t="s">
+        <v>433</v>
+      </c>
+      <c r="N50" t="s">
+        <v>31</v>
+      </c>
+      <c r="O50" t="s">
+        <v>32</v>
+      </c>
+      <c r="P50" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>443</v>
+      </c>
+      <c r="R50" t="s">
+        <v>444</v>
+      </c>
+      <c r="S50" t="s">
+        <v>445</v>
+      </c>
+      <c r="T50" t="s">
+        <v>23</v>
+      </c>
+      <c r="U50" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="51" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>447</v>
+      </c>
+      <c r="B51" t="s">
+        <v>258</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" t="s">
+        <v>158</v>
+      </c>
+      <c r="G51" t="s">
+        <v>159</v>
+      </c>
+      <c r="H51" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51" t="s">
+        <v>448</v>
+      </c>
+      <c r="K51" t="s">
+        <v>449</v>
+      </c>
+      <c r="L51" t="s">
+        <v>90</v>
+      </c>
+      <c r="M51" t="s">
+        <v>433</v>
+      </c>
+      <c r="N51" t="s">
+        <v>31</v>
+      </c>
+      <c r="O51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P51" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>451</v>
+      </c>
+      <c r="R51" t="s">
+        <v>452</v>
+      </c>
+      <c r="S51" t="s">
+        <v>453</v>
+      </c>
+      <c r="T51" t="s">
+        <v>23</v>
+      </c>
+      <c r="U51" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="52" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>454</v>
+      </c>
+      <c r="B52" t="s">
+        <v>258</v>
+      </c>
+      <c r="C52" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" t="s">
+        <v>25</v>
+      </c>
+      <c r="H52" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J52" t="s">
+        <v>455</v>
+      </c>
+      <c r="K52" t="s">
+        <v>456</v>
+      </c>
+      <c r="L52" t="s">
+        <v>90</v>
+      </c>
+      <c r="M52" t="s">
+        <v>457</v>
+      </c>
+      <c r="N52" t="s">
+        <v>31</v>
+      </c>
+      <c r="O52" t="s">
+        <v>32</v>
+      </c>
+      <c r="P52" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>458</v>
+      </c>
+      <c r="R52" t="s">
+        <v>459</v>
+      </c>
+      <c r="S52" t="s">
+        <v>460</v>
+      </c>
+      <c r="T52" t="s">
+        <v>23</v>
+      </c>
+      <c r="U52" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="53" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>461</v>
+      </c>
+      <c r="B53" t="s">
+        <v>439</v>
+      </c>
+      <c r="C53" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" t="s">
+        <v>25</v>
+      </c>
+      <c r="H53" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" t="s">
+        <v>26</v>
+      </c>
+      <c r="J53" t="s">
+        <v>462</v>
+      </c>
+      <c r="K53" t="s">
+        <v>463</v>
+      </c>
+      <c r="L53" t="s">
+        <v>90</v>
+      </c>
+      <c r="M53" t="s">
+        <v>464</v>
+      </c>
+      <c r="N53" t="s">
+        <v>31</v>
+      </c>
+      <c r="O53" t="s">
+        <v>32</v>
+      </c>
+      <c r="P53" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>466</v>
+      </c>
+      <c r="R53" t="s">
+        <v>467</v>
+      </c>
+      <c r="S53" t="s">
+        <v>468</v>
+      </c>
+      <c r="T53" t="s">
+        <v>23</v>
+      </c>
+      <c r="U53" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="54" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>469</v>
+      </c>
+      <c r="B54" t="s">
+        <v>258</v>
+      </c>
+      <c r="C54" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" t="s">
+        <v>470</v>
+      </c>
+      <c r="G54" t="s">
+        <v>471</v>
+      </c>
+      <c r="H54" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54" t="s">
+        <v>472</v>
+      </c>
+      <c r="K54" t="s">
+        <v>473</v>
+      </c>
+      <c r="L54" t="s">
+        <v>90</v>
+      </c>
+      <c r="M54" t="s">
+        <v>464</v>
+      </c>
+      <c r="N54" t="s">
+        <v>31</v>
+      </c>
+      <c r="O54" t="s">
+        <v>32</v>
+      </c>
+      <c r="P54" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>475</v>
+      </c>
+      <c r="R54" t="s">
+        <v>476</v>
+      </c>
+      <c r="S54" t="s">
+        <v>477</v>
+      </c>
+      <c r="T54" t="s">
+        <v>23</v>
+      </c>
+      <c r="U54" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="55" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>478</v>
+      </c>
+      <c r="B55" t="s">
+        <v>479</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" t="s">
+        <v>25</v>
+      </c>
+      <c r="H55" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" t="s">
+        <v>26</v>
+      </c>
+      <c r="J55" t="s">
+        <v>480</v>
+      </c>
+      <c r="K55" t="s">
+        <v>481</v>
+      </c>
+      <c r="L55" t="s">
+        <v>90</v>
+      </c>
+      <c r="M55" t="s">
+        <v>464</v>
+      </c>
+      <c r="N55" t="s">
+        <v>69</v>
+      </c>
+      <c r="O55" t="s">
+        <v>32</v>
+      </c>
+      <c r="P55" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>483</v>
+      </c>
+      <c r="R55" t="s">
+        <v>217</v>
+      </c>
+      <c r="S55" t="s">
+        <v>125</v>
+      </c>
+      <c r="T55" t="s">
+        <v>23</v>
+      </c>
+      <c r="U55" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="56" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>485</v>
+      </c>
+      <c r="B56" t="s">
+        <v>258</v>
+      </c>
+      <c r="C56" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" t="s">
+        <v>25</v>
+      </c>
+      <c r="H56" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" t="s">
+        <v>26</v>
+      </c>
+      <c r="J56" t="s">
+        <v>486</v>
+      </c>
+      <c r="K56" t="s">
+        <v>487</v>
+      </c>
+      <c r="L56" t="s">
+        <v>90</v>
+      </c>
+      <c r="M56" t="s">
+        <v>464</v>
+      </c>
+      <c r="N56" t="s">
+        <v>31</v>
+      </c>
+      <c r="O56" t="s">
+        <v>32</v>
+      </c>
+      <c r="P56" t="s">
+        <v>488</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>489</v>
+      </c>
+      <c r="R56" t="s">
+        <v>490</v>
+      </c>
+      <c r="S56" t="s">
+        <v>491</v>
+      </c>
+      <c r="T56" t="s">
+        <v>23</v>
+      </c>
+      <c r="U56" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="57" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>492</v>
+      </c>
+      <c r="B57" t="s">
+        <v>479</v>
+      </c>
+      <c r="C57" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" t="s">
+        <v>26</v>
+      </c>
+      <c r="J57" t="s">
+        <v>493</v>
+      </c>
+      <c r="K57" t="s">
+        <v>494</v>
+      </c>
+      <c r="L57" t="s">
+        <v>90</v>
+      </c>
+      <c r="M57" t="s">
+        <v>495</v>
+      </c>
+      <c r="N57" t="s">
+        <v>69</v>
+      </c>
+      <c r="O57" t="s">
+        <v>32</v>
+      </c>
+      <c r="P57" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>497</v>
+      </c>
+      <c r="R57" t="s">
+        <v>498</v>
+      </c>
+      <c r="S57" t="s">
+        <v>125</v>
+      </c>
+      <c r="T57" t="s">
+        <v>23</v>
+      </c>
+      <c r="U57" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>499</v>
+      </c>
+      <c r="B59" t="s">
+        <v>479</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" t="s">
+        <v>24</v>
+      </c>
+      <c r="G59" t="s">
+        <v>25</v>
+      </c>
+      <c r="H59" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" t="s">
+        <v>26</v>
+      </c>
+      <c r="J59" t="s">
+        <v>500</v>
+      </c>
+      <c r="K59" t="s">
+        <v>501</v>
+      </c>
+      <c r="L59" t="s">
+        <v>90</v>
+      </c>
+      <c r="M59" t="s">
+        <v>502</v>
+      </c>
+      <c r="N59" t="s">
+        <v>69</v>
+      </c>
+      <c r="O59" t="s">
+        <v>32</v>
+      </c>
+      <c r="P59" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>504</v>
+      </c>
+      <c r="R59" t="s">
+        <v>505</v>
+      </c>
+      <c r="S59" t="s">
+        <v>125</v>
+      </c>
+      <c r="T59" t="s">
+        <v>23</v>
+      </c>
+      <c r="U59" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>506</v>
+      </c>
+      <c r="B60" t="s">
+        <v>479</v>
+      </c>
+      <c r="C60" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" t="s">
+        <v>24</v>
+      </c>
+      <c r="G60" t="s">
+        <v>25</v>
+      </c>
+      <c r="H60" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" t="s">
+        <v>26</v>
+      </c>
+      <c r="J60" t="s">
+        <v>507</v>
+      </c>
+      <c r="K60" t="s">
+        <v>508</v>
+      </c>
+      <c r="L60" t="s">
+        <v>90</v>
+      </c>
+      <c r="M60" t="s">
+        <v>502</v>
+      </c>
+      <c r="N60" t="s">
+        <v>69</v>
+      </c>
+      <c r="O60" t="s">
+        <v>32</v>
+      </c>
+      <c r="P60" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>510</v>
+      </c>
+      <c r="R60" t="s">
+        <v>256</v>
+      </c>
+      <c r="S60" t="s">
+        <v>125</v>
+      </c>
+      <c r="T60" t="s">
+        <v>23</v>
+      </c>
+      <c r="U60" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>511</v>
+      </c>
+      <c r="B61" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61" t="s">
+        <v>313</v>
+      </c>
+      <c r="G61" t="s">
+        <v>314</v>
+      </c>
+      <c r="H61" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" t="s">
+        <v>26</v>
+      </c>
+      <c r="J61" t="s">
+        <v>512</v>
+      </c>
+      <c r="K61" t="s">
+        <v>513</v>
+      </c>
+      <c r="L61" t="s">
+        <v>90</v>
+      </c>
+      <c r="M61" t="s">
+        <v>514</v>
+      </c>
+      <c r="N61" t="s">
+        <v>31</v>
+      </c>
+      <c r="O61" t="s">
+        <v>32</v>
+      </c>
+      <c r="P61" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>515</v>
+      </c>
+      <c r="R61" t="s">
+        <v>59</v>
+      </c>
+      <c r="S61" t="s">
+        <v>23</v>
+      </c>
+      <c r="T61" t="s">
+        <v>23</v>
+      </c>
+      <c r="U61" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>517</v>
+      </c>
+      <c r="B62" t="s">
+        <v>258</v>
+      </c>
+      <c r="C62" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" t="s">
+        <v>518</v>
+      </c>
+      <c r="K62" t="s">
+        <v>519</v>
+      </c>
+      <c r="L62" t="s">
+        <v>90</v>
+      </c>
+      <c r="M62" t="s">
+        <v>520</v>
+      </c>
+      <c r="N62" t="s">
+        <v>31</v>
+      </c>
+      <c r="O62" t="s">
+        <v>32</v>
+      </c>
+      <c r="P62" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>522</v>
+      </c>
+      <c r="R62" t="s">
+        <v>523</v>
+      </c>
+      <c r="S62" t="s">
+        <v>524</v>
+      </c>
+      <c r="T62" t="s">
+        <v>23</v>
+      </c>
+      <c r="U62" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>525</v>
+      </c>
+      <c r="B63" t="s">
+        <v>167</v>
+      </c>
+      <c r="C63" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" t="s">
+        <v>25</v>
+      </c>
+      <c r="H63" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" t="s">
+        <v>26</v>
+      </c>
+      <c r="J63" t="s">
+        <v>526</v>
+      </c>
+      <c r="K63" t="s">
+        <v>527</v>
+      </c>
+      <c r="L63" t="s">
+        <v>90</v>
+      </c>
+      <c r="M63" t="s">
+        <v>520</v>
+      </c>
+      <c r="N63" t="s">
+        <v>69</v>
+      </c>
+      <c r="O63" t="s">
+        <v>32</v>
+      </c>
+      <c r="P63" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>529</v>
+      </c>
+      <c r="R63" t="s">
+        <v>256</v>
+      </c>
+      <c r="S63" t="s">
+        <v>23</v>
+      </c>
+      <c r="T63" t="s">
+        <v>23</v>
+      </c>
+      <c r="U63" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>530</v>
+      </c>
+      <c r="B64" t="s">
+        <v>212</v>
+      </c>
+      <c r="C64" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" t="s">
+        <v>25</v>
+      </c>
+      <c r="H64" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" t="s">
+        <v>26</v>
+      </c>
+      <c r="J64" t="s">
+        <v>531</v>
+      </c>
+      <c r="K64" t="s">
+        <v>532</v>
+      </c>
+      <c r="L64" t="s">
+        <v>90</v>
+      </c>
+      <c r="M64" t="s">
+        <v>520</v>
+      </c>
+      <c r="N64" t="s">
+        <v>69</v>
+      </c>
+      <c r="O64" t="s">
+        <v>32</v>
+      </c>
+      <c r="P64" t="s">
+        <v>533</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>255</v>
+      </c>
+      <c r="R64" t="s">
+        <v>534</v>
+      </c>
+      <c r="S64" t="s">
+        <v>23</v>
+      </c>
+      <c r="T64" t="s">
+        <v>23</v>
+      </c>
+      <c r="U64" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>535</v>
+      </c>
+      <c r="B65" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" t="s">
+        <v>470</v>
+      </c>
+      <c r="G65" t="s">
+        <v>471</v>
+      </c>
+      <c r="H65" t="s">
+        <v>23</v>
+      </c>
+      <c r="I65" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65" t="s">
+        <v>536</v>
+      </c>
+      <c r="K65" t="s">
+        <v>537</v>
+      </c>
+      <c r="L65" t="s">
+        <v>90</v>
+      </c>
+      <c r="M65" t="s">
+        <v>538</v>
+      </c>
+      <c r="N65" t="s">
+        <v>31</v>
+      </c>
+      <c r="O65" t="s">
+        <v>32</v>
+      </c>
+      <c r="P65" t="s">
+        <v>539</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>540</v>
+      </c>
+      <c r="R65" t="s">
+        <v>299</v>
+      </c>
+      <c r="S65" t="s">
+        <v>541</v>
+      </c>
+      <c r="T65" t="s">
+        <v>23</v>
+      </c>
+      <c r="U65" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>542</v>
+      </c>
+      <c r="B66" t="s">
+        <v>51</v>
+      </c>
+      <c r="C66" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" t="s">
+        <v>25</v>
+      </c>
+      <c r="H66" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" t="s">
+        <v>26</v>
+      </c>
+      <c r="J66" t="s">
+        <v>543</v>
+      </c>
+      <c r="K66" t="s">
+        <v>544</v>
+      </c>
+      <c r="L66" t="s">
+        <v>90</v>
+      </c>
+      <c r="M66" t="s">
+        <v>538</v>
+      </c>
+      <c r="N66" t="s">
+        <v>31</v>
+      </c>
+      <c r="O66" t="s">
+        <v>32</v>
+      </c>
+      <c r="P66" t="s">
+        <v>545</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>546</v>
+      </c>
+      <c r="R66" t="s">
+        <v>299</v>
+      </c>
+      <c r="S66" t="s">
+        <v>547</v>
+      </c>
+      <c r="T66" t="s">
+        <v>23</v>
+      </c>
+      <c r="U66" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>548</v>
+      </c>
+      <c r="B67" t="s">
+        <v>51</v>
+      </c>
+      <c r="C67" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67" t="s">
+        <v>24</v>
+      </c>
+      <c r="G67" t="s">
+        <v>25</v>
+      </c>
+      <c r="H67" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" t="s">
+        <v>26</v>
+      </c>
+      <c r="J67" t="s">
+        <v>549</v>
+      </c>
+      <c r="K67" t="s">
+        <v>550</v>
+      </c>
+      <c r="L67" t="s">
+        <v>90</v>
+      </c>
+      <c r="M67" t="s">
+        <v>538</v>
+      </c>
+      <c r="N67" t="s">
+        <v>31</v>
+      </c>
+      <c r="O67" t="s">
+        <v>32</v>
+      </c>
+      <c r="P67" t="s">
+        <v>551</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>552</v>
+      </c>
+      <c r="R67" t="s">
+        <v>553</v>
+      </c>
+      <c r="S67" t="s">
+        <v>554</v>
+      </c>
+      <c r="T67" t="s">
+        <v>23</v>
+      </c>
+      <c r="U67" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>555</v>
+      </c>
+      <c r="B68" t="s">
+        <v>556</v>
+      </c>
+      <c r="C68" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" t="s">
+        <v>23</v>
+      </c>
+      <c r="F68" t="s">
+        <v>557</v>
+      </c>
+      <c r="G68" t="s">
+        <v>558</v>
+      </c>
+      <c r="H68" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" t="s">
+        <v>243</v>
+      </c>
+      <c r="J68" t="s">
+        <v>559</v>
+      </c>
+      <c r="K68" t="s">
+        <v>560</v>
+      </c>
+      <c r="L68" t="s">
+        <v>90</v>
+      </c>
+      <c r="M68" t="s">
+        <v>538</v>
+      </c>
+      <c r="N68" t="s">
+        <v>31</v>
+      </c>
+      <c r="O68" t="s">
+        <v>32</v>
+      </c>
+      <c r="P68" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>561</v>
+      </c>
+      <c r="R68" t="s">
+        <v>189</v>
+      </c>
+      <c r="S68" t="s">
+        <v>562</v>
+      </c>
+      <c r="U68" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>564</v>
+      </c>
+      <c r="B69" t="s">
+        <v>556</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" t="s">
+        <v>565</v>
+      </c>
+      <c r="G69" t="s">
+        <v>566</v>
+      </c>
+      <c r="H69" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" t="s">
+        <v>243</v>
+      </c>
+      <c r="J69" t="s">
+        <v>567</v>
+      </c>
+      <c r="K69" t="s">
+        <v>568</v>
+      </c>
+      <c r="L69" t="s">
+        <v>90</v>
+      </c>
+      <c r="M69" t="s">
+        <v>538</v>
+      </c>
+      <c r="N69" t="s">
+        <v>31</v>
+      </c>
+      <c r="O69" t="s">
+        <v>32</v>
+      </c>
+      <c r="P69" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>569</v>
+      </c>
+      <c r="R69" t="s">
+        <v>189</v>
+      </c>
+      <c r="S69" t="s">
+        <v>570</v>
+      </c>
+      <c r="U69" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="71" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>571</v>
+      </c>
+      <c r="B71" t="s">
+        <v>167</v>
+      </c>
+      <c r="C71" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71" t="s">
+        <v>24</v>
+      </c>
+      <c r="G71" t="s">
+        <v>25</v>
+      </c>
+      <c r="H71" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" t="s">
+        <v>26</v>
+      </c>
+      <c r="J71" t="s">
+        <v>572</v>
+      </c>
+      <c r="K71" t="s">
+        <v>573</v>
+      </c>
+      <c r="L71" t="s">
+        <v>90</v>
+      </c>
+      <c r="M71" t="s">
+        <v>574</v>
+      </c>
+      <c r="N71" t="s">
+        <v>69</v>
+      </c>
+      <c r="O71" t="s">
+        <v>32</v>
+      </c>
+      <c r="P71" t="s">
+        <v>575</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>576</v>
+      </c>
+      <c r="R71" t="s">
+        <v>256</v>
+      </c>
+      <c r="S71" t="s">
+        <v>125</v>
+      </c>
+      <c r="T71" t="s">
+        <v>23</v>
+      </c>
+      <c r="U71" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="72" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>577</v>
+      </c>
+      <c r="B72" t="s">
+        <v>258</v>
+      </c>
+      <c r="C72" t="s">
+        <v>23</v>
+      </c>
+      <c r="D72" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" t="s">
+        <v>23</v>
+      </c>
+      <c r="F72" t="s">
+        <v>578</v>
+      </c>
+      <c r="G72" t="s">
+        <v>579</v>
+      </c>
+      <c r="H72" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" t="s">
+        <v>52</v>
+      </c>
+      <c r="J72" t="s">
+        <v>580</v>
+      </c>
+      <c r="K72" t="s">
+        <v>581</v>
+      </c>
+      <c r="L72" t="s">
+        <v>90</v>
+      </c>
+      <c r="M72" t="s">
+        <v>582</v>
+      </c>
+      <c r="N72" t="s">
+        <v>31</v>
+      </c>
+      <c r="O72" t="s">
+        <v>32</v>
+      </c>
+      <c r="P72" t="s">
+        <v>583</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>584</v>
+      </c>
+      <c r="R72" t="s">
+        <v>585</v>
+      </c>
+      <c r="S72" t="s">
+        <v>586</v>
+      </c>
+      <c r="T72" t="s">
+        <v>23</v>
+      </c>
+      <c r="U72" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="73" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>587</v>
+      </c>
+      <c r="B73" t="s">
+        <v>258</v>
+      </c>
+      <c r="C73" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G73" t="s">
+        <v>588</v>
+      </c>
+      <c r="H73" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" t="s">
+        <v>26</v>
+      </c>
+      <c r="J73" t="s">
+        <v>589</v>
+      </c>
+      <c r="K73" t="s">
+        <v>590</v>
+      </c>
+      <c r="L73" t="s">
+        <v>90</v>
+      </c>
+      <c r="M73" t="s">
+        <v>582</v>
+      </c>
+      <c r="N73" t="s">
+        <v>31</v>
+      </c>
+      <c r="O73" t="s">
+        <v>32</v>
+      </c>
+      <c r="P73" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>592</v>
+      </c>
+      <c r="R73" t="s">
+        <v>593</v>
+      </c>
+      <c r="S73" t="s">
+        <v>594</v>
+      </c>
+      <c r="T73" t="s">
+        <v>23</v>
+      </c>
+      <c r="U73" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="74" ht="14.45" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>595</v>
+      </c>
+      <c r="B74" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" t="s">
+        <v>23</v>
+      </c>
+      <c r="D74" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74" t="s">
+        <v>110</v>
+      </c>
+      <c r="G74" t="s">
+        <v>111</v>
+      </c>
+      <c r="H74" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" t="s">
+        <v>26</v>
+      </c>
+      <c r="J74" t="s">
+        <v>596</v>
+      </c>
+      <c r="K74" t="s">
+        <v>289</v>
+      </c>
+      <c r="L74" t="s">
+        <v>90</v>
+      </c>
+      <c r="M74" t="s">
+        <v>597</v>
+      </c>
+      <c r="N74" t="s">
+        <v>31</v>
+      </c>
+      <c r="O74" t="s">
+        <v>32</v>
+      </c>
+      <c r="P74" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>291</v>
+      </c>
+      <c r="R74" t="s">
+        <v>217</v>
+      </c>
+      <c r="S74" t="s">
+        <v>598</v>
+      </c>
+      <c r="T74" t="s">
+        <v>23</v>
+      </c>
+      <c r="U74" t="s">
+        <v>293</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>